--- a/context_DB/HTI_context_db.xlsx
+++ b/context_DB/HTI_context_db.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK141"/>
+  <dimension ref="A1:BL141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -681,65 +681,70 @@
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
+          <t>fatalities</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>event_count_evt2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>ADM1_PCODE_evt2</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>ADM3_PCODE_evt2</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>event_type</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>sub_event_type</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>actor1</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_1</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>actor2</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>assoc_actor_2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>event_date</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
           <t>admin2</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>fatalities</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>event_count_evt2</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>ADM3_PCODE_evt2</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>event_type</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>sub_event_type</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>actor1</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_1</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>actor2</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>assoc_actor_2</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>event_date</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>ratio IDP/ToTN - HPC2025</t>
         </is>
@@ -762,7 +767,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -842,59 +847,64 @@
           <t>Ouest</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Port-au-Prince</t>
-        </is>
+      <c r="AY2" t="n">
+        <v>96</v>
       </c>
       <c r="AZ2" t="n">
-        <v>88</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>58</v>
+        <v>61</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>HT01</t>
+        </is>
       </c>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>Strategic developments ---- Strategic developments ---- Strategic developments ---- Explosions/Remote violence ---- Violence against civilians ---- Battles ---- Battles ---- Violence against civilians ---- Battles ---- Battles ---- Protests ---- Battles ---- Violence against civilians ---- Violence against civilians ---- Protests ---- Strategic developments ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Protests ---- Violence against civilians ---- Violence against civilians ---- Battles ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Strategic developments ---- Battles ---- Battles ---- Battles ---- Battles ---- Battles ---- Strategic developments ---- Violence against civilians ---- Strategic developments ---- Battles ---- Battles ---- Battles ---- Battles ---- Battles ---- Violence against civilians ---- Battles ---- Battles ---- Violence against civilians ---- Violence against civilians ---- Protests ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Strategic developments ---- Battles ---- Battles ---- Battles ---- Riots ---- Strategic developments ---- Violence against civilians ---- Violence against civilians ---- Protests</t>
+          <t>Protests ---- Violence against civilians ---- Violence against civilians ---- Strategic developments ---- Riots ---- Battles ---- Battles ---- Battles ---- Strategic developments ---- Violence against civilians ---- Violence against civilians ---- Protests ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Battles ---- Battles ---- Violence against civilians ---- Battles ---- Battles ---- Battles ---- Battles ---- Battles ---- Violence against civilians ---- Strategic developments ---- Strategic developments ---- Battles ---- Battles ---- Battles ---- Battles ---- Battles ---- Strategic developments ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Battles ---- Violence against civilians ---- Violence against civilians ---- Protests ---- Violence against civilians ---- Violence against civilians ---- Violence against civilians ---- Strategic developments ---- Protests ---- Violence against civilians ---- Battles ---- Violence against civilians ---- Protests ---- Battles ---- Battles ---- Violence against civilians ---- Battles ---- Battles ---- Violence against civilians ---- Explosions/Remote violence ---- Strategic developments ---- Strategic developments ---- Strategic developments ---- Violence against civilians ---- Protests ---- Protests</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>Looting/property destruction ---- Other ---- Other ---- Air/drone strike ---- Sexual violence ---- Armed clash ---- Armed clash ---- Attack ---- Armed clash ---- Armed clash ---- Peaceful protest ---- Armed clash ---- Attack ---- Attack ---- Peaceful protest ---- Other ---- Abduction/forced disappearance ---- Abduction/forced disappearance ---- Abduction/forced disappearance ---- Peaceful protest ---- Attack ---- Attack ---- Armed clash ---- Attack ---- Attack ---- Attack ---- Looting/property destruction ---- Armed clash ---- Armed clash ---- Armed clash ---- Armed clash ---- Armed clash ---- Looting/property destruction ---- Attack ---- Looting/property destruction ---- Armed clash ---- Armed clash ---- Armed clash ---- Armed clash ---- Armed clash ---- Attack ---- Armed clash ---- Armed clash ---- Attack ---- Abduction/forced disappearance ---- Peaceful protest ---- Abduction/forced disappearance ---- Abduction/forced disappearance ---- Abduction/forced disappearance ---- Other ---- Armed clash ---- Armed clash ---- Armed clash ---- Violent demonstration ---- Other ---- Sexual violence ---- Abduction/forced disappearance ---- Peaceful protest</t>
+          <t>Peaceful protest ---- Abduction/forced disappearance ---- Sexual violence ---- Other ---- Violent demonstration ---- Armed clash ---- Armed clash ---- Armed clash ---- Other ---- Abduction/forced disappearance ---- Abduction/forced disappearance ---- Peaceful protest ---- Abduction/forced disappearance ---- Abduction/forced disappearance ---- Attack ---- Armed clash ---- Armed clash ---- Attack ---- Armed clash ---- Armed clash ---- Armed clash ---- Armed clash ---- Armed clash ---- Attack ---- Looting/property destruction ---- Looting/property destruction ---- Armed clash ---- Armed clash ---- Armed clash ---- Armed clash ---- Armed clash ---- Looting/property destruction ---- Attack ---- Attack ---- Attack ---- Armed clash ---- Attack ---- Attack ---- Peaceful protest ---- Abduction/forced disappearance ---- Abduction/forced disappearance ---- Abduction/forced disappearance ---- Other ---- Peaceful protest ---- Attack ---- Armed clash ---- Attack ---- Peaceful protest ---- Armed clash ---- Armed clash ---- Attack ---- Armed clash ---- Armed clash ---- Sexual violence ---- Air/drone strike ---- Other ---- Other ---- Looting/property destruction ---- Attack ---- Peaceful protest ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>Unidentified Gang (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Police Forces of Haiti (2024-) ---- Viv Ansanm Gang ---- Police Forces of Haiti (2024-) Protected Areas Security Brigade (BSAP) ---- Grand-Ravine Gang ---- Grand-Ravine Gang ---- Police Forces of Haiti (2024-) ---- Kraze Barye Gang ---- Protesters (Haiti) ---- Police Forces of Haiti (2024-) ---- Unidentified Gang (Haiti) ---- Base 5 Secondes Gang ---- Protesters (Haiti) ---- Unidentified Armed Group (Haiti) ---- Unidentified Armed Group (Haiti) ---- Unidentified Armed Group (Haiti) ---- Unidentified Gang (Haiti) ---- Protesters (Haiti) ---- G-9 Gang ---- Unidentified Gang (Haiti) ---- Grand-Ravine Gang ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Armed Group (Haiti) ---- Unidentified Armed Group (Haiti) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Viv Ansanm Gang ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Base 5 Secondes Gang ---- G-9 Gang ---- G-9 Gang ---- G-9 Gang ---- G-9 Gang ---- Unidentified Gang (Haiti) ---- Protesters (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Protesters (Haiti) ---- Unidentified Gang (Haiti) ---- 400 Mawozo Gang ---- 400 Mawozo Gang ---- Rioters (Haiti) ---- Civilians (Haiti) ---- Terre Noire Gang ---- Grand-Ravine Gang ---- Protesters (Haiti)</t>
+          <t>Protesters (Haiti) ---- Grand-Ravine Gang ---- Terre Noire Gang ---- Protesters (Haiti) ---- Rioters (Haiti) ---- 400 Mawozo Gang ---- 400 Mawozo Gang ---- Unidentified Gang (Haiti) ---- Protesters (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Protesters (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- G-9 Gang ---- G-9 Gang ---- G-9 Gang ---- G-9 Gang ---- Base 5 Secondes Gang ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Viv Ansanm Gang ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Unidentified Armed Group (Haiti) ---- Unidentified Armed Group (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Grand-Ravine Gang ---- Unidentified Gang (Haiti) ---- G-9 Gang ---- Protesters (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Armed Group (Haiti) ---- Unidentified Armed Group (Haiti) ---- Unidentified Armed Group (Haiti) ---- Protesters (Haiti) ---- Base 5 Secondes Gang ---- Police Forces of Haiti (2024-) ---- Unidentified Gang (Haiti) ---- Protesters (Haiti) ---- Police Forces of Haiti (2024-) ---- Kraze Barye Gang ---- Grand-Ravine Gang ---- Grand-Ravine Gang ---- Police Forces of Haiti (2024-) Protected Areas Security Brigade (BSAP) ---- Viv Ansanm Gang ---- Police Forces of Haiti (2024-) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Armed Group (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti)</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>Unidentified Communal Militia (Haiti) ---- Base 5 Secondes Gang; Viv Ansanm Gang ---- Base 5 Secondes Gang; Viv Ansanm Gang ---- Students (Haiti) ---- Grand-Ravine Gang; Ti Bwa Gang; Viv Ansanm Gang; Didi Gang ---- Teachers (Haiti) ---- Students (Haiti) ---- Bout Ba Gang ---- Military Forces of Haiti (2017-2024) ---- G-9 Gang ---- Students (Haiti) ---- BSAC: Anti-Corruption Union Brigade ---- BSAC: Anti-Corruption Union Brigade; CNOHA: National Coordination for Haitian Workers; Labor Group (Haiti); National Awakening for the Sovereingty of Haiti ---- Health Workers (Haiti); Students (Haiti)</t>
+          <t>Health Workers (Haiti); Students (Haiti) ---- BSAC: Anti-Corruption Union Brigade; CNOHA: National Coordination for Haitian Workers; Labor Group (Haiti); National Awakening for the Sovereingty of Haiti ---- BSAC: Anti-Corruption Union Brigade ---- Students (Haiti) ---- G-9 Gang ---- Military Forces of Haiti (2017-2024) ---- Bout Ba Gang ---- Students (Haiti) ---- Teachers (Haiti) ---- Didi Gang; Grand-Ravine Gang; Ti Bwa Gang; Viv Ansanm Gang ---- Students (Haiti) ---- Base 5 Secondes Gang; Viv Ansanm Gang ---- Base 5 Secondes Gang; Viv Ansanm Gang ---- Unidentified Communal Militia (Haiti) ---- Teachers (Haiti) ---- Labor Group (Haiti)</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>Civilians (Haiti) ---- Unidentified Gang (Haiti) ---- Civilians (Haiti) ---- Unidentified Gang (Haiti) ---- Police Forces of Haiti (2024-) ---- Civilians (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Communal Militia (Haiti) ---- Unidentified Gang (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Police Forces of Haiti (2017-2024) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Viv Ansanm Gang ---- Viv Ansanm Gang ---- Base 5 Secondes Gang ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Civilians (Haiti) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Unidentified Gang (Haiti) ---- Kraze Barye Gang ---- Kraze Barye Gang ---- Civilians (Haiti) ---- Civilians (Haiti)</t>
+          <t>Civilians (Haiti) ---- Civilians (Haiti) ---- Kraze Barye Gang ---- Kraze Barye Gang ---- Unidentified Gang (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Civilians (Haiti) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Police Forces of Haiti (2017-2024) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Base 5 Secondes Gang ---- Viv Ansanm Gang ---- Viv Ansanm Gang ---- Unidentified Gang (Haiti) ---- Unidentified Gang (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Police Forces of Haiti (2017-2024) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti) ---- Unidentified Gang (Haiti) ---- Civilians (Haiti) ---- Unidentified Gang (Haiti) ---- Unidentified Communal Militia (Haiti) ---- Civilians (Haiti) ---- Police Forces of Haiti (2024-) ---- Unidentified Gang (Haiti) ---- Civilians (Haiti) ---- Unidentified Gang (Haiti) ---- Civilians (Haiti) ---- Civilians (Haiti)</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>Catholic Christian Group (Haiti); Students (Haiti) ---- Women (Haiti) ---- Refugees/IDPs (Haiti) ---- Military Forces of Haiti (2024-); Police Forces of Haiti (2024-) ---- Protestant Christian Group (Haiti); Students (Haiti) ---- Government of Haiti (2024-) ---- Police Forces of Haiti (2017-2024); Women (Haiti) ---- Teachers (Haiti) ---- Labor Group (Haiti) ---- Labor Group (Haiti) ---- Labor Group (Haiti) ---- Labor Group (Haiti) ---- Students (Haiti) ---- Women (Haiti) ---- Catholic Christian Group (Haiti); Teachers (Haiti) ---- Catholic Christian Group (Haiti); Journalists (Haiti) ---- Catholic Christian Group (Haiti) ---- Teachers (Haiti) ---- Women (Haiti) ---- Catholic Christian Group (Haiti); Taxi/Bus Drivers (Haiti); Teachers (Haiti); Women (Haiti)</t>
+          <t>Catholic Christian Group (Haiti); Taxi/Bus Drivers (Haiti); Teachers (Haiti); Women (Haiti) ---- Women (Haiti) ---- Teachers (Haiti) ---- Catholic Christian Group (Haiti); Teachers (Haiti) ---- Catholic Christian Group (Haiti); Journalists (Haiti) ---- Catholic Christian Group (Haiti) ---- Students (Haiti) ---- Women (Haiti) ---- Labor Group (Haiti) ---- Labor Group (Haiti) ---- Labor Group (Haiti) ---- Labor Group (Haiti) ---- Teachers (Haiti) ---- Police Forces of Haiti (2017-2024); Women (Haiti) ---- Government of Haiti (2024-) ---- Protestant Christian Group (Haiti); Students (Haiti) ---- Military Forces of Haiti (2024-); Police Forces of Haiti (2024-) ---- Refugees/IDPs (Haiti) ---- Women (Haiti) ---- Catholic Christian Group (Haiti); Students (Haiti) ---- Women (Haiti); Health Workers (Haiti)</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>Looting: On 26 April 2025, in Port-au-Prince - Pacot, Ouest, more than 15 armed gang members occupied and vandalized the Catholic Saint-Francois d'Assise High School, located on Rue 6 (Pacot). The criminals recorded a video dressed in students' clothes. ---- Other: On 14 April 2025, in Port-au-Prince, Ouest, a roadblock was set up in Canape-Vert. Another was also set up on the Martin Luther King Avenue from the Natcom offices (in Bois Patate) to the Canado school (Debussy/Haut-Turgeau). The roadblocks were still present on 15 April. There is no information on the motives for the roadblocks or who set them up. ---- Other: On 26 March 2025, in Petionville, Ouest, a roadblock of tires was set up on the road near the Union School (Juvenat neighborhood), where the presence of the police was registered. Another roadblock was also registered in Thomassin 32. There is no information on the circumstances or motives of the roadblocks. ---- On 19 March 2025, in Port-au-Prince - STEP/Eglise Baptiste de Bolosse, Ouest, the police dropped explosive drones over the territories of several gangs near the Maranatha Evangelical School. This action was also carried out in the downtown area, near Fort-Mercredi, Martissant, Grand Ravine, as well as Delmas 30 neighborhoods (coded separately). In March, police drone airstrike and armed clashes were drones were used resulted in at least 115 gang members killed and 119 injured. At least 115 fatalities split across 19 events. 6 coded here. ---- On 14 March 2025, in Port-au-Prince - Bas Peu de Choses, Ouest, the Viv Ansanm Gang attacked residents on Marcellin, Cameau, and Capois streets. They looted several buildings, including the Infopac School. Other buildings were set on fire. The criminals fired shots and raped a 16-year-old girl. People fled the area. The French Embassy, on Capois street, closed its doors due to gang-related violence in the area. They also targeted nearby areas of the Avenue Christophe neighborhood (coded separately). Casualties unknown. ---- On 13 March 2025, in Gressier - La Salle Pte Place, Ouest, BSAP agents supported by members of the population carrying machetes killed four gang members out of a group of 103 occupying the premises of the Peres Salesians de Don Bosco School, located in la Colline area. The BSAP agents shot and killed a security guard suspected of being collaborating with the criminals. 5 fatalities. ---- On 11 March 2025, in Port-au-Prince - Bas Peu de Choses, Ouest, the Grand-Ravine Gang and the Base 5 Secondes Gang (in support of the Viv Ansanm Gang) clashed with police forces in Place Jeremie as the criminals attacked residential areas between Place Jeremie, Jean Jacques Dessalines School, and close areas to the Oloffson hotel. Several residents' houses and vehicles were set on fire on Capois, Romain, Chavannes, and Magloire Ambroise streets. Gunshots were heard at the height of Christophe and N Avenues. Many residents fled their homes to take refuge elsewhere. Casualties unknown. ---- On 10 March 2025, in Port-au-Prince - Bas Peu de Choses, Ouest, the Grand-Ravine Gang and the Base 5 Secondes Gang (affiliates of the Viv Ansanm Gang coalition) deployed along the Chavannes street and opened fire on the temporary shelter at a Girl's High School, killing a civilian and injuring two others. The victims were part of a group of displaced residents taking shelter at the mentioned institution. Viv Ansanm Gang members also set fire to buildings along the Capois and Alerte streets, and on the Christophe Avenue, killing and injuring several civilians. At least 1 fatality, at least 2 injured. ---- On 24 February 2025, in Gressier - La Salle Pte Place, Ouest, police forces shot and killed five gang members during clashes in La Salle Pte Place and Lafferonay areas, close to the Don Bosco Salesians School. Three firearms were seized by the police. Clashes were also registered in nearby La Colline area (Gressier) and Flon (Leogane) (coded separately). 5 fatalities. ---- On 24 February 2025, in Tabarre - Tabarre 27, Ouest, overnight, the Kraze Barye Gang attacked the positions of a self-defense group brigade in Tabarre 27 and 25, prompting clashes with the police, who intervened to expel them. During the offensive, the gangsters set fire to residents' houses. A local morgue held up to 15 bodies. At least four were identified (two men and a woman whose bodies were found on the streets, and a former high school head and executive of the Ministry of Education man killed and burned at his home). A military officer was shot and injured. At least 15 fatalities, 1 injured. ---- Around 19 February 2025 (between 17 - 21 February), in Port-au-Prince - Champs de Mars, Ouest, students from the Faculty of Medicine and Pharmacy of the State University held a march demanding a new headquarters for the General Hospital for them to continue their studies. ---- On 11 February 2025, in Port-au-Prince - Bourdon, Ouest, police forces engaged in armed clashes with gang members. A male student who was on this way to the Centre for Diplomatic and International Studies (CEDI), in Bourdon, was shot and killed by a stray bullet. 1 fatality. ---- On 11 February 2025, in Delmas - St Louis de Gonzague- Henfrasa -Palais de l'art, Ouest, gunshots were heard. A student at the Saint-Louis de Gonzague school was shot and injured by a stray bullet. This was likely part of gang-related attack, as gang engaged in gunfights with police in several neighborhoods in Port-au-Prince on that day (coded separately). 1 injured. ---- On 28 January 2025, in the Kenscoff commune, Ouest, gang members attacked residents and set fire to properties in several areas including Krevites (a.k.a. Prevites), Kikwa (a.k.a. Qui-Croit), Nan Pitimi, Chauffard, Sous Rozo, and Grande Source. Only in Kikwa, 10 students from the Baptist Haiti Mission and two women (described as wives of employees at the mission) were killed as the gangs took over a church and a school, turning them into a gang headquarters. A woman living with physical deficiency was also killed. Between Krevites and Kikwa areas, a pastor from the Christian Brotherhood Union Church and seven family members were killed. This was part of a coordinated armed offensive by the Base 5 Secondes Gang, the Grand-Ravine Gang, and the Ti Bwa Gang (affiliates of the Viv Ansanm Gang) against the Kenscoff commune (coded separately). A report clarified that the offensive was linked to a plan led by the Didi Gang to take control of the close Petionville commune. Between 26 and 30 January, at least 127 civilians had been killed by gangs in Kenscoff and Petionville during the attacks of the Viv Ansanm Gang (up to 150 according to some sources though most of these fatalities remain unconfirmed). At least 127 fatalities split across 26 events. 21 fatalities coded for this event. ---- On 16 January 2025, in Port-au-Prince - Musseau-Delmas 48, Ouest, a group of teachers held a sit-in protest in front of the Ministry of National Education and Vocational Training (MENFP), in Musseau-Delmas 48 neighborhood, demanding better working conditions. The mobilization was part of a teachers' labor strike. ---- Other: On 1 December 2024, in Port-au-Prince, Ouest, gunshots were heard on Charles Sumner Avenue and near the Sacre Coeur school (Turgeau neighborhood). There is no information on the circumstances or authorship of the gunshots. ---- On 8 November 2024, in Delmas - Puits Blain, Ouest, an unknown number of individuals kidnapped two schoolchildren as they were on their way to the school centre. Their whereabouts are unknown. There is no information on the perpetrators and circumstances of the abduction, but the latest reports suggest that most abductions are gang-related. ---- On 11 October 2024, in Port-au-Prince - Turgeau, Ouest, an unknown number of people were kidnapped near a school. Although there is no information on the circumstances or perpetrators, latest reports suggest that most abductions are gang-related. Another report indicates that the kidnapping attempt might have been stopped by the police. The victims' whereabouts are unknown. ---- On 22 July 2024, in Gressier, Ouest, armed gang members kidnapped a man at his home and asked for the payment of a ransom to his family as a condition for his release. The victim, who was a public worker at the National Equipment Centre (CNE) and a math's teacher, was not liberated despite the payment of the ransom. The victim's family claimed to have been attacked by the gang members as they contacted the police for help (coded separately). The victim's whereabouts are unknown. ---- On 4 July 2024, in Delmas - Delmas 48, Ouest, intern students from the ENS School held a sit-in protest in front of the Ministry of National Education and Vocational Training (MENFP), in Delmas 48 neighbourhood, to demand the payment of their internships. ---- On 10 June 2024, in Port-au-Prince - Delmas, Ouest, in the morning, the leader of the G-9 Gang launched an attack and set fire to several houses and schools in the commune. Casualties unknown. ---- On 29 May 2024, in Port-au-Prince - Bas Peu de Choses, Ouest, in the morning, armed gang members on a motorcycle shot and killed a teacher man and head of the School 'Sisters Saint Mary of the Angels' on the Capois street, where the institution is located (Bas Peu de Choses neighbourhood) (drive-by). The victim was said to be driving next to the school when he got shot and lost the control of the vehicle, crashing with a house. According to several sources, the shooting happened as the victim tried to resist a kidnapping attempt. The perpetrators fled the scene. 1 fatality. ---- On 10 May 2024, in Gressier - Cite Gressier, Ouest, overnight, armed members of the Grand-Ravine Gang set fire to the Gressier police station (Cite Gressier neighbourhood). A police vehicle, the houses of an assessor mayor, and a police, as well as a school building were also burned. Police forces intervened and clashed with the gang members in the vicinity of the police station, although they were unable to expel the criminals, who took control of the facility. A police officer was shot and injured. A public transport driver and several civilians were wounded by the bullets. In Bo Lanme area, a 53-year-old woman was killed in front of her two minor daughters at her home. The girls were later raped by the gang members. In Colombier 9 area, gang members looted a property and stole some items. Members of the Bout Ba Gang also participated in the clashes near the Gressier market, and a man was shot and killed as he received a gunshot to the head. Thousands of residents fled their homes to take refuge elsewhere. The gang members are part of the Living Together gang-led initiative. During the offensive, which last until 11 May, several of them were recorded expressing their rejection to the Multilateral Support Security Mission (MMSS). On 12 May, police forces, supported by the Miragoane police commissioner, and BSAP agents, regained control of the police station after the gang members had abandoned it. At least 2 fatalities, at least 2 injured. ---- On 8 May 2024, in Port-au-Prince - Bois Verna, Ouest, in the morning, armed gang members shot and killed a police officer woman as she tried to resist a kidnapping attempt, on the Camille Leon Street (in Bois Verna neighbourhood). The attack took place moments after the officer had left her girl at school (likely off-duty). The attackers stole the officer's firearm and fled the scene on a motorcycle. 1 fatality. ---- Around 29 April 2024 (week of), in Port-au-Prince - Centre Ville, Ouest, armed gang members attacked the Foyer Saint-Vincent facilities (a.k.a. Saint Vicent School for Disabled Children), located on the Paul VI street, in Centre Ville neighbourhood. An unknown number of disabled people (mostly children) were forced to flee the building. Casualties unknown. ---- On 23 April 2024, in Port-au-Prince - Bas Peu de Choses, Ouest, in the morning, an unknown number of armed individuals attacked the head of the Jean-Jacques Dessalines high school on the Christophe Avenue (in Bas Peu de Choses neighbourhood). The victim was injured to the head (nature of the wounds unspecified). The motivation for the attack is unknown. 1 injured. ---- Property destruction: Around 11 April 2024 (week of), in Port-au-Prince - Cathedrale, Ouest, armed group members looted and set fire to the JB Damier Vocational School. Some items were stolen. ---- On 8 April 2024, in Port-au-Prince - Champs de Mars, Ouest, police forces clashed with gang members in the vicinity of the National Palace as the gangsters attacked civilian facilities in the area and around, including the Bird School on the Enterrement street, in Centre Ville neighbourhood (coded separately). Material damages were mentioned at the school. Police forces used megaphones to inform citizens to leave the area. Gunshots were heard throughout the day in Nazon and Lalue neighborhoods, as well as in other areas such as Alerte street, Sylvio Cator Stadium (Morne a Tuf neighborhood), Marche Salomon (Bas Peu de Choses neighborhood), Bolosse Avenue. Casualties unknown. ---- On 8 April 2024, in Port-au-Prince - Centre Ville, Ouest, gang members attacked civilian facilities in the area and around, including the Bird School on the Enterrement street. Material damages were mentioned at the school. Police forces used megaphones to inform citizens to leave the area. Because of that, police forces clashed with gang members in the vicinity of the National Palace in the Champs de Mars neighbourhood (coded separately). Gunshots were heard throughout the day in Nazon and Lalue neighborhoods, as well as in other areas such as Alerte street, Sylvio Cator Stadium (Morne a Tuf neighborhood), Marche Salomon (Bas Peu de Choses neighborhood), Bolosse Avenue. Casualties unknown. ---- On 2 April 2024, in Port-au-Prince - Champs de Mars, Ouest, police forces clashed with gang members in the vicinity of the National Palace as these ones opened fire on the institution. A number of gangsters entered the premises of the Haiti State University Hospital (HUEH) (a.k.a. Port-au-Prince General Hospital) and shot at the officers from the hospital's facilities. Smoke rose from the Finance Ministry building. Police forces fired tear gas to disperse the scores of civilians who were nearby. During clashes, a moto taxi driver was shot and killed by a stray bullet in front of the Blaise Pascal School, in Bois Verna neighbourhood (coded separately). Gunshots were also heard in Christ-Roi. The gang members were described as affiliates of the Living Together gang-led coalition (Viv Ansanm gang). No casualties. ---- On 2 April 2024, in Port-au-Prince - Bois Verna, Ouest, police forces clashed with gang members and a man was shot and killed by a stray bullet in front of the Blaise Pascal School. The victim was a moto taxi driver. Gunshots were also heard in Christ-Roi. The gang members were described as affiliates of the Living Together gang-led coalition (Viv Ansanm gang). Clashes also took place in Champs de Mars neighborhood (coded separately). 1 fatality. ---- On 1 April 2024, in Port-au-Prince - Champs de Mars, Ouest, police and military forces clashed with the Base 5 Secondes Gang near the National Palace. During clashes, the gang members set fire to a police armored vehicle on the Monseigneur Guilloux street, injuring at least four officers who were inside. Scores of civilians got trapped amidst the crossfire. A person whose body was found on the street with gunshot wounds was likely to have been killed in the crossfire. The armed gangsters looted and robbed the National Library (Centre-Ville neighbourhood). They also entered the Saint-Martial Minor Seminary School (Poste Marchand), burned several vehicles and destroyed some materials, although no casualties among the present colleagues were mentioned. Gunshots were heard on Lamarre street, and on Capois street, as well as in Christ-Roi coming from Nazon. The gang members were described as affiliates of the Living Together gang-led coalition led by the G-9 Gang. At least 1 fatality, at least 4 injured. ---- Property destruction: On 27 March 2024, in Port-au-Prince - Canape-Vert, Ouest, the Viv Ansanm Gang set fire to the Superior Normal School (ENS) facilities. It is known that the building was unoccupied when the attack took place. ---- On 25 March 2024, in Port-au-Prince - Morne a Tuf, Ouest, gang members attacked, looted, and set fire to several buildings on the Monseigneur Guilloux street, including at least five pharmacies, several private clinics, an unspecified number of private residences, business establishments, and several vehicles. The National School of Arts (in Morne a Tuf) was looted and some works were stolen. At least one person was killed. His/her dead body was found lying on the street. At least 1 fatality. ---- Property destruction: On 25 March 2024, in Carrefour - Fontamara Est, Ouest, gang members set fire to the Freres Nau Mixed School. ---- On 18 March 2024, in Petion Ville - Laboule, Ouest, police forces clashed with gang members as they attacked residents, private properties, and companies' facilities in Laboule, Thomassin (coded separately), Boutilliers (coded separately), and Pelerin neighborhoods (coded separately). Around a dozen people were killed and several were injured. One fatal victim was a woman described as the head of Women's Classical School. A bank branch, a gas station, and several houses were attacked and looted, including that of a judge at the Superior Court of Auditors and Administrative Litigation, who had been evacuated before the attack (in Laboule 18). In Laboule 12, gunshots were heard as the gangsters stole some vehicles. The criminals had arrived in three vehicles. Other versions stated that they used four trucks and 27 motorcycles. Several injured, at least 12 fatalities, split across 4 events, 3 fatalities coded. ---- On 18 March 2024, in Petion Ville - Thomassin, Ouest, police forces clashed with gang members as they attacked residents, private properties, and companies' facilities in Laboule (coded separately), Thomassin, Boutilliers (coded separately), and Pelerin neighborhoods (coded separately). Around a dozen people were killed and several were injured. One fatal victim was a woman described as the head of Women's Classical School. A bank branch, a gas station, and several houses were attacked and looted, including that of a judge at the Superior Court of Auditors and Administrative Litigation, who had been evacuated before the attack (in Laboule 18). In Laboule 12, gunshots were heard as the gangsters stole some vehicles. The criminals had arrived in three vehicles. Other versions stated that they used four trucks and 27 motorcycles. Several injured, at least 12 fatalities, split across 4 events, 3 fatalities coded. ---- On 18 March 2024, in Petion Ville - Boutilliers, Ouest, police forces clashed with gang members as they attacked residents, private properties, and companies' facilities in Laboule (coded separately), Thomassin (coded separately), Boutilliers, and Pelerin neighborhoods (coded separately). Around a dozen people were killed and several were injured. One fatal victim was a woman described as the head of Women's Classical School. A bank branch, a gas station, and several houses were attacked and looted, including that of a judge at the Superior Court of Auditors and Administrative Litigation, who had been evacuated before the attack (in Laboule 18). In Laboule 12, gunshots were heard as the gangsters stole some vehicles. The criminals had arrived in three vehicles. Other versions stated that they used four trucks and 27 motorcycles. Several injured, at least 12 fatalities, split across 4 events, 3 fatalities coded. ---- On 18 March 2024, in Petion Ville - Pelerin, Ouest, police forces clashed with gang members as they attacked residents, private properties, and companies' facilities in Laboule (coded separately), Thomassin (coded separately), Boutilliers (coded separately), and Pelerin neighborhoods. Around a dozen people were killed and several were injured. One fatal victim was a woman described as the head of Women's Classical School. A bank branch, a gas station, and several houses were attacked and looted, including that of a judge at the Superior Court of Auditors and Administrative Litigation, who had been evacuated before the attack (in Laboule 18). In Laboule 12, gunshots were heard as the gangsters stole some vehicles. The criminals had arrived in three vehicles. Other versions stated that they used four trucks and 27 motorcycles. Several injured, at least 12 fatalities, split across 4 events, 3 fatalities coded. ---- On 8 March 2024, in Port-au-Prince - Champs de Mars, Ouest, for the second consecutive day, police forces clashed with members of the Base 5 Secondes Gang (a.k.a. Village de Dieu Gang) as they attacked the National Palace and three police stations in Champs de Mars. Several gang members and people (unspecified affiliation) were killed. An unknown number of police officers were killed and injured. The criminals set fire to several vehicles at the Ministry of the Interior and Territorial Communities (Champs de Mars), although the police intervention prevented the burning of the building. In Bas Peu de Choses, the Ministry of National Education and Vocational Training (MENFP) was looted. Gunshots were heard in Turgeau, Poste Marchand, Pacot, Lalue, Canape-Vert, and Nazon. The attack on the National Palace was part of coordinated attacks by the G-9 Gang leader and the Living Together Movement gang-led initiative. Unspecified number of fatalities coded as 3. ---- On 29 February 2024, in Cite Soleil - Damiens/Macaya, Ouest, gang members (likely G-9 Gang members due to ongoing coordinated attacks) attacked the Ministry of the Agriculture and occupied the Agronomy and Veterinary Medicine Faculty (UEH University), in Damiens neighbourhood. Students were taken as hostages. One student was shot and injured in the ear, while a young girl was grazed by a bullet. This was part of a set of coordinated attacks led by the G-9 Gang leader, who claimed responsibility, and supported by gangs aligned to the Living Together Movement gang-led initiative. The G-9 leader was seen in a video announcing his intentions of seizing the police chief and government ministers and preventing Prime Minister (PM), Ariel Henry, from returning to Haiti. The PM was in Kenya on a government visit. 1 injured. ---- On 29 February 2024, in Port-au-Prince - Morne a Tuf, Ouest, gang members (likely G-9 members due to ongoing coordinated attacks) clashed with police forces as they set fire to several houses in Saint-Honore Street (Morne a Tuf), and they burned the Portail Leogane police station (coded separately). The gangsters also occupied the Sylvio Castor National Stadium (Morne a Tuf) and kidnapped an employee. His whereabouts are unknown. Gunshots were heard in Bicentenaire, Carrefour-Feuilles, Bel Air, Bas Delmas, Post Marchand, Champs de Mars, and Morne a Tuf areas. An Education Centre on Allerte Street was vandalized while two trader women were killed on the Magloire Amboise Avenue (Bas Peu de Choses, coded separately). At least 25 people injured by the bullets were received in the Haiti State University Hospital (Morne a Tuf). Two of the wounded died. This was part of a set of coordinated attacks led by the G-9 Gang leader, who claimed responsibility, and supported by gangs aligned to the Living Together Movement gang-led initiative (coded separately). The G-9 leader was seen in a video announcing his intentions of seizing the police chief and government ministers and preventing Prime Minister (PM), Ariel Henry, from returning to Haiti. The PM was in Kenya on a government visit. At least 23 injured, and least 2 fatalities, split across 2 events. ---- On 29 February 2024, in Port-au-Prince - Portail Leogane/Cite Louverture, Ouest, gang members (likely G-9 members due to ongoing coordinated attacks) burned the Portail Leogane police station. One source stated that the building was empty when the arson attack took place. A different version stated that some officers were inside, although they were not injured. Clashes with police forces also took place in Saint-Honore Street (Morne a Tuf, coded separately). Gunshots were heard in Bicentenaire, Carrefour-Feuilles, Bel Air, Bas Delmas, Post Marchand, Champs de Mars, and Morne a Tuf areas. An Education Centre on Allerte Street was vandalized while two trader women were killed on the Magloire Amboise Avenue (Bas Peu de Choses, coded separately). At least 25 people injured by the bullets were received in the Haiti State University Hospital (Morne a Tuf). Two of the wounded died. This was part of a set of coordinated attacks led by the G-9 Gang leader, who claimed responsibility, and supported by gangs aligned to the Living Together Movement gang-led initiative (coded separately). The G-9 leader was seen in a video announcing his intentions of seizing the police chief and government ministers and preventing Prime Minister (PM), Ariel Henry, from returning to Haiti. The PM was in Kenya on a government visit. At least 23 injured, and least 2 fatalities, split across 2 events. ---- On 29 February 2024, in Port-au-Prince - Bas Peu De Choses, Ouest, an Education Centre on Allerte Street was vandalized while two trader women were killed on the Magloire Amboise Avenue (Bas Peu de Choses) by gang members (likely G-9 members due to ongoing coordinated attacks). Clashes between the gang and police forces also took place in Saint-Honore Street (Morne a Tuf, coded separately), and they burned the Portail Leogane police station (coded separately). Gunshots were heard in Bicentenaire, Carrefour-Feuilles, Bel Air, Bas Delmas, Post Marchand, Champs de Mars, and Morne a Tuf areas. At least 25 people injured by the bullets were received in the Haiti State University Hospital (Morne a Tuf). Two of the wounded died. This was part of a set of coordinated attacks led by the G-9 Gang leader, who claimed responsibility, and supported by gangs aligned to the Living Together Movement gang-led initiative (coded separately). The G-9 leader was seen in a video announcing his intentions of seizing the police chief and government ministers and preventing Prime Minister (PM), Ariel Henry, from returning to Haiti. The PM was in Kenya on a government visit. 2 fatalities. ---- On 23 February 2024, in Port-au-Prince - Morne a Tuf, Ouest, armed gang members kidnapped six Brothers of the Sacred Heart Congregation and a teacher near the Jean XXIII School (Catholic Christian Group), in Morne a Tuf neighbourhood. The abductors asked for a ransom as a condition for their release. In another area a Catholic priest and 10 other people were kidnapped in the capital, including two cameramen from Tele Amen (coded separately). Around 9 March 2024, the mentioned teacher and four Brothers of the Sacred Heart Congregation were released. The other two religious Brothers were released on 26 March under unknown circumstances. ---- Around 23 February 2024 (as reported), in Port-au-Prince, Ouest, students from the Law and Economic Sciences Faculty (FDSE) and other UEH entities held a protest with banners and set up barricades near the UEH university (nature unspecified) demanding the liberation of a teacher who was kidnapped around 17 February (coded separately). ---- On 23 February 2024, in Port-au-Prince, Ouest, two cameramen from Tele Amen (Christian media outlet) were kidnapped in an unspecified location of the city. Armed gang members kidnapped also kidnapped a Catholic priest in Port-au-Prince - Portail Saint Joseph (coded separately) and Six Brothers of the Sacred Heart Congregation and a teacher in Morne a Tuf neighbourhood (coded separately). ---- On 23 February 2024, in Port-au-Prince - Portail Saint Joseph, Ouest, armed gang members kidnapped a Catholic priest near Notre Dame de Fatima Chapel. Six Brothers of the Sacred Heart Congregation and a teacher were also kidnapped in Morne a Tuf neighbourhood (coded separately). On the same day, up to 10 people were kidnapped in the capital, including two cameramen from Tele Amen (Christian media outlet) (coded separately). ---- Around 17 February 2024 (between 15 - 19 February), in Port-au-Prince - Bicentenaire, Ouest, gang members abducted a man in the Bicentenaire neighbourhood. The victim was a teacher at the Faculty of Law and Economic Sciences. His whereabouts are unknown. ---- Strikes: On 5 February 2024, in Port-au-Prince, Ouest, the Anti-Corruption Union Brigade (BSAC) called on two days of nationwide general strike (until 6 February) to demand that national authorities provide solutions to the security crisis in Haiti. As a consequence, school activities were suspended in several locations across Haiti as anti-government mobilizations continued on 5 February. This was the second strike called by the BSAC after the one called on 29 January (coded separately). ---- On 31 January 2024, in Port-au-Prince, Ouest, rival gang members engaged in armed clashes in several neighborhoods, including Lalue area. During clashes, a stray bullet entered the premises of the Sainte Rose de Lima school, although no one was injured. The institution suspended its activity after this. Casualties unknown. ---- On 30 January 2024, in Petion Ville - Pernier, Ouest, the 400 Mawozo Gang engaged in armed clashes with members of the Vitelhomme Gang (a.k.a. Kraze Barye Gang) in Pernier and Freres neighborhoods (coded separately). Only in Pernier, at least four people were killed. Between 30 and 31 January, a dozen civilians were killed and an unknown number were injured by the gangsters. Among the wounded, there was a man who was shot while picking up his son from school. Several hundred residents left their homes and took refuge elsewhere. At least 10 fatalities split across 3 events, 4 fatalities coded. ---- On 30 January 2024, in Petion Ville - Freres, Ouest, the 400 Mawozo Gang engaged in armed clashes with members of the Vitelhomme Gang (a.k.a. Kraze Barye Gang) in Pernier (coded separately) and Freres neighborhoods. Only in Pernier, at least four people were killed. Between 30 and 31 January, a dozen civilians were killed and an unknown number were injured by the gangsters. Among the wounded, there was a man who was shot while picking up his son from school. Several hundred residents left their homes and took refuge elsewhere. At least 10 fatalities split across 3 events, 3 fatalities coded. ---- On 29 January 2024, in Port-au-Prince, Ouest, residents held a demonstration demanding the departure of Prime Minister, Ariel Henry. They set up barricades of burning tires on Martin Luther King Avenue, among others. Commercial and school activities were paralyzed. The demonstration, which was part of anti-government mobilizations called by Guy Philippe (a former police officer, senator, convict, paramilitary leader, and warlord who had called on taking the streets and leading a revolution in Haiti), was held on the first day of nationwide general strike called by organizations from the political opposition (coded separately). ---- Strikes: On 28 January 2024, in the arrondissement of Port-au-Prince, Ouest, the National Awakening for the Sovereignty of Haiti movement (led by Guy Philippe), together with the Anti-Corruption Union Brigade (BSAC), and the National Coordination of Haitian Workers (CNOHA), called on three days of nationwide general strike as of 29 January to demand that national authorities provide solutions to the security crisis in Haiti. As a consequence, school activities were suspended in several locations across Haiti as anti-government mobilizations continued on 29 January. The strike was suspended on 30 January due to the lack of support throughout the national territory (transport and commercial activities did not paralyze). ---- On 26 January 2024, in Cite Soleil - Brooklyn, Ouest, members of the Terre Noire Gang raped a 17-year-old girl several times and shot and killed her as she was on her way to school through a road outside the Brooklyn neighbourhood. 1 fatality. ---- On 19 January 2024, in Port-au-Prince, Ouest, in the morning, armed members of the Grand-Ravine Gang kidnapped six nuns (women) belonging to the Saint Anne Sisters Catholic Congregation from a bus, on the Chili Avenue. The bus driver and a teacher were also abducted. Kidnappers asked for a ransom of 3 million dollars. The victims were released on 24 January under unclarified circumstances. ---- On 9 January 2024, in Port-au-Prince, Ouest, health workers, students, and patients from the GHESKIO h</t>
+          <t>On 9 January 2024, in Port-au-Prince, Ouest, health workers, students, and patients from the GHESKIO health centers, as well as relatives, held a sit-in protest with banners at the institution's facilities (Bicentenaire neighborhood) to demand the release of a doctor who had been kidnapped on 28 November (coded separately). The abducted is the son of the GHESKIO health center's owner. ---- On 19 January 2024, in Port-au-Prince - Saint Gerard, Ouest, in the morning, armed members of the Grand-Ravine Gang kidnapped six nuns (women) belonging to the Saint Anne Sisters Catholic Congregation from a bus, on the Chili Avenue. The bus driver and a teacher were also abducted. One source identified the abductors are Base 5 Secondes affiliates, although no other media backed this. Kidnappers asked for a ransom of 3 million dollars. The victims were released on 24 January under unclarified circumstances. ---- On 26 January 2024, in Cite Soleil - Brooklyn, Ouest, members of the Terre Noire Gang raped a 17-year-old girl several times and shot and killed her as she was on her way to school through a road outside the Brooklyn neighbourhood. 1 fatality. ---- Strikes: On 28 January 2024, in the arrondissement of Port-au-Prince, Ouest, the National Awakening for the Sovereignty of Haiti movement (led by Guy Philippe), together with the Anti-Corruption Union Brigade (BSAC), and the National Coordination of Haitian Workers (CNOHA), called on three days of nationwide general strike as of 29 January to demand that national authorities provide solutions to the security crisis in Haiti. As a consequence, school activities were suspended in several locations across Haiti as anti-government mobilizations continued on 29 January. The strike was suspended on 30 January due to the lack of support throughout the national territory (transport and commercial activities did not paralyze). ---- On 29 January 2024, in Port-au-Prince, Ouest, residents held a demonstration demanding the departure of Prime Minister, Ariel Henry. They set up barricades of burning tires on Martin Luther King Avenue, among others. Commercial and school activities were paralyzed. The demonstration, which was part of anti-government mobilizations called by Guy Philippe (a former police officer, senator, convict, paramilitary leader, and warlord who had called on taking the streets and leading a revolution in Haiti), was held on the first day of nationwide general strike called by organizations from the political opposition (coded separately). ---- On 30 January 2024, in Petion Ville - Freres, Ouest, the 400 Mawozo Gang engaged in armed clashes with members of the Vitelhomme Gang (a.k.a. Kraze Barye Gang) in Pernier (coded separately) and Freres neighborhoods. Only in Pernier, at least four people were killed (coded separately). Between 30 and 31 January, dozens of civilians were killed and an unknown number were injured by the gangsters in Petionville. Among the wounded, there was a man who was shot while picking up his son from school. Several hundred residents left their homes and took refuge elsewhere. Unspecified number of fatalities coded as 3. ---- On 30 January 2024, in Petion Ville - Pernier, Ouest, the 400 Mawozo Gang engaged in armed clashes with members of the Vitelhomme Gang (a.k.a. Kraze Barye Gang) in Pernier and Freres neighborhoods (coded separately). Only in Pernier, at least four people were killed. A school teacher got his eyes gouged by the Kraze Barye Gang. Between 30 and 31 January, a dozen civilians were killed and an unknown number were injured by the gangsters in Petionville. Among the wounded, there was a man who was shot while picking up his son from school. Several hundred residents left their homes and took refuge elsewhere. At least 4 fatalities. ---- On 31 January 2024, in Port-au-Prince, Ouest, rival gang members engaged in armed clashes in several neighborhoods, including Lalue area. During clashes, a stray bullet entered the premises of the Sainte Rose de Lima school, although no one was injured. The institution suspended its activity after this. Casualties unknown. ---- Strikes: On 5 February 2024, in Port-au-Prince, Ouest, the Anti-Corruption Union Brigade (BSAC) called on two days of nationwide general strike (until 6 February) to demand that national authorities provide solutions to the security crisis in Haiti. As a consequence, school activities were suspended in several locations across Haiti as anti-government mobilizations continued on 5 February. This was the second strike called by the BSAC after the one called on 29 January (coded separately). ---- Around 17 February 2024 (between 15 - 19 February), in Port-au-Prince - Bicentenaire, Ouest, gang members abducted a man in the Bicentenaire neighbourhood. The victim was a teacher at the Faculty of Law and Economic Sciences. His whereabouts are unknown. ---- On 23 February 2024, in Port-au-Prince - Morne a Tuf, Ouest, armed gang members kidnapped six Brothers of the Sacred Heart Congregation and a teacher near the Jean XXIII School (Catholic Christian Group), in Morne a Tuf neighbourhood. The abductors asked for a ransom as a condition for their release. In another area a Catholic priest and 10 other people were kidnapped in the capital, including two cameramen from Tele Amen (coded separately). Around 9 March 2024, the mentioned teacher and four Brothers of the Sacred Heart Congregation were released. The other two religious Brothers were released on 26 March under unknown circumstances. ---- Around 23 February 2024 (as reported), in Port-au-Prince, Ouest, students from the Law and Economic Sciences Faculty (FDSE) and other UEH entities held a protest with banners and set up barricades near the UEH university (nature unspecified) demanding the liberation of a teacher who was kidnapped around 17 February (coded separately). ---- On 23 February 2024, in Port-au-Prince, Ouest, two cameramen from Tele Amen (Christian media outlet) were kidnapped in an unspecified location of the city. Armed gang members kidnapped also kidnapped a Catholic priest in Port-au-Prince - Portail Saint Joseph (coded separately) and Six Brothers of the Sacred Heart Congregation and a teacher in Morne a Tuf neighbourhood (coded separately). ---- On 23 February 2024, in Port-au-Prince - Portail Saint Joseph, Ouest, armed gang members kidnapped a Catholic priest near Notre Dame de Fatima Chapel. Six Brothers of the Sacred Heart Congregation and a teacher were also kidnapped in Morne a Tuf neighbourhood (coded separately). On the same day, up to 10 people were kidnapped in the capital, including two cameramen from Tele Amen (Christian media outlet) (coded separately). ---- On 29 February 2024, in Cite Soleil - Damiens/Macaya, Ouest, gang members (likely G-9 Gang members due to ongoing coordinated attacks) attacked the Ministry of the Agriculture and occupied the Agronomy and Veterinary Medicine Faculty (UEH University), in Damiens neighbourhood. Students were taken as hostages. One student was shot and injured in the ear, while a young girl was grazed by a bullet. This was part of a set of coordinated attacks led by the G-9 Gang leader, who claimed responsibility, and supported by gangs aligned to the Living Together Movement gang-led initiative. The G-9 leader was seen in a video announcing his intentions of seizing the police chief and government ministers and preventing Prime Minister (PM), Ariel Henry, from returning to Haiti. The PM was in Kenya on a government visit. 1 injured. ---- On 29 February 2024, in Port-au-Prince - Morne a Tuf, Ouest, gang members (likely G-9 members due to ongoing coordinated attacks) clashed with police forces as they set fire to several houses in Saint-Honore Street (Morne a Tuf), and they burned the Portail Leogane police station (coded separately). The gangsters also occupied the Sylvio Castor National Stadium (Morne a Tuf) and kidnapped an employee. His whereabouts are unknown. Gunshots were heard in Bicentenaire, Carrefour-Feuilles, Bel Air, Bas Delmas, Post Marchand, Champs de Mars, and Morne a Tuf areas. An Education Centre on Allerte Street was vandalized while two trader women were killed on the Magloire Amboise Avenue (Bas Peu de Choses, coded separately). At least 25 people injured by the bullets were received in the Haiti State University Hospital (Morne a Tuf). Two of the wounded died. This was part of a set of coordinated attacks led by the G-9 Gang leader, who claimed responsibility, and supported by gangs aligned to the Living Together Movement gang-led initiative (coded separately). The G-9 leader was seen in a video announcing his intentions of seizing the police chief and government ministers and preventing Prime Minister (PM), Ariel Henry, from returning to Haiti. The PM was in Kenya on a government visit. At least 23 injured, and least 2 fatalities, split across 2 events. ---- On 29 February 2024, in Port-au-Prince - Portail Leogane/Cite Louverture, Ouest, gang members (likely G-9 members due to ongoing coordinated attacks) burned the Portail Leogane police station. One source stated that the building was empty when the arson attack took place. A different version stated that some officers were inside, although they were not injured. Clashes with police forces also took place in Saint-Honore Street (Morne a Tuf, coded separately). Gunshots were heard in Bicentenaire, Carrefour-Feuilles, Bel Air, Bas Delmas, Post Marchand, Champs de Mars, and Morne a Tuf areas. An Education Centre on Allerte Street was vandalized while two trader women were killed on the Magloire Amboise Avenue (Bas Peu de Choses, coded separately). At least 25 people injured by the bullets were received in the Haiti State University Hospital (Morne a Tuf). Two of the wounded died. This was part of a set of coordinated attacks led by the G-9 Gang leader, who claimed responsibility, and supported by gangs aligned to the Living Together Movement gang-led initiative (coded separately). The G-9 leader was seen in a video announcing his intentions of seizing the police chief and government ministers and preventing Prime Minister (PM), Ariel Henry, from returning to Haiti. The PM was in Kenya on a government visit. At least 23 injured, and least 2 fatalities, split across 2 events. ---- On 29 February 2024, in Port-au-Prince - Bas Peu De Choses, Ouest, an Education Centre on Allerte Street was vandalized while two trader women were killed on the Magloire Amboise Avenue (Bas Peu de Choses) by gang members (likely G-9 members due to ongoing coordinated attacks). Clashes between the gang and police forces also took place in Saint-Honore Street (Morne a Tuf, coded separately), and they burned the Portail Leogane police station (coded separately). Gunshots were heard in Bicentenaire, Carrefour-Feuilles, Bel Air, Bas Delmas, Post Marchand, Champs de Mars, and Morne a Tuf areas. At least 25 people injured by the bullets were received in the Haiti State University Hospital (Morne a Tuf). Two of the wounded died. This was part of a set of coordinated attacks led by the G-9 Gang leader, who claimed responsibility, and supported by gangs aligned to the Living Together Movement gang-led initiative (coded separately). The G-9 leader was seen in a video announcing his intentions of seizing the police chief and government ministers and preventing Prime Minister (PM), Ariel Henry, from returning to Haiti. The PM was in Kenya on a government visit. 2 fatalities. ---- On 8 March 2024, in Port-au-Prince - Champs de Mars, Ouest, for the second consecutive day, police forces clashed with members of the Base 5 Secondes Gang (a.k.a. Village de Dieu Gang) as they attacked the National Palace and three police stations in Champs de Mars. Several gang members and people (unspecified affiliation) were killed. An unknown number of police officers were killed and injured. The criminals set fire to several vehicles at the Ministry of the Interior and Territorial Communities (Champs de Mars), although the police intervention prevented the burning of the building. In Bas Peu de Choses, the Ministry of National Education and Vocational Training (MENFP) was looted. Gunshots were heard in Turgeau, Poste Marchand, Pacot, Lalue, Canape-Vert, and Nazon. The attack on the National Palace was part of coordinated attacks by the G-9 Gang leader and the Living Together Movement gang-led initiative. Unspecified number of fatalities coded as 3. ---- On 18 March 2024, in Petion Ville - Laboule, Ouest, police forces clashed with gang members as they attacked residents, private properties, and companies' facilities in Laboule, Thomassin (coded separately), Boutilliers (coded separately), and Pelerin neighborhoods (coded separately). Around a dozen people were killed and several were injured. One fatal victim was a woman described as the head of Women's Classical School. A bank branch, a gas station, and several houses were attacked and looted, including that of a judge at the Superior Court of Auditors and Administrative Litigation, who had been evacuated before the attack (in Laboule 18). In Laboule 12, gunshots were heard as the gangsters stole some vehicles. The criminals had arrived in three vehicles. Other versions stated that they used four trucks and 27 motorcycles. Several injured, at least 12 fatalities, split across 4 events, 3 fatalities coded. ---- On 18 March 2024, in Petion Ville - Thomassin, Ouest, police forces clashed with gang members as they attacked residents, private properties, and companies' facilities in Laboule (coded separately), Thomassin, Boutilliers (coded separately), and Pelerin neighborhoods (coded separately). Around a dozen people were killed and several were injured. One fatal victim was a woman described as the head of Women's Classical School. A bank branch, a gas station, and several houses were attacked and looted, including that of a judge at the Superior Court of Auditors and Administrative Litigation, who had been evacuated before the attack (in Laboule 18). In Laboule 12, gunshots were heard as the gangsters stole some vehicles. The criminals had arrived in three vehicles. Other versions stated that they used four trucks and 27 motorcycles. Several injured, at least 12 fatalities, split across 4 events, 3 fatalities coded. ---- On 18 March 2024, in Petion Ville - Boutilliers, Ouest, police forces clashed with gang members as they attacked residents, private properties, and companies' facilities in Laboule (coded separately), Thomassin (coded separately), Boutilliers, and Pelerin neighborhoods (coded separately). Around a dozen people were killed and several were injured. One fatal victim was a woman described as the head of Women's Classical School. A bank branch, a gas station, and several houses were attacked and looted, including that of a judge at the Superior Court of Auditors and Administrative Litigation, who had been evacuated before the attack (in Laboule 18). In Laboule 12, gunshots were heard as the gangsters stole some vehicles. The criminals had arrived in three vehicles. Other versions stated that they used four trucks and 27 motorcycles. Several injured, at least 12 fatalities, split across 4 events, 3 fatalities coded. ---- On 18 March 2024, in Petion Ville - Pelerin, Ouest, police forces clashed with gang members as they attacked residents, private properties, and companies' facilities in Laboule (coded separately), Thomassin (coded separately), Boutilliers (coded separately), and Pelerin neighborhoods. Around a dozen people were killed and several were injured. One fatal victim was a woman described as the head of Women's Classical School. A bank branch, a gas station, and several houses were attacked and looted, including that of a judge at the Superior Court of Auditors and Administrative Litigation, who had been evacuated before the attack (in Laboule 18). In Laboule 12, gunshots were heard as the gangsters stole some vehicles. The criminals had arrived in three vehicles. Other versions stated that they used four trucks and 27 motorcycles. Several injured, at least 12 fatalities, split across 4 events, 3 fatalities coded. ---- On 25 March 2024, in Port-au-Prince - Morne a Tuf, Ouest, gang members attacked, looted, and set fire to several buildings on the Monseigneur Guilloux street, including at least five pharmacies, several private clinics, an unspecified number of private residences, business establishments, and several vehicles. The National School of Arts (in Morne a Tuf) was looted and some works were stolen. At least one person was killed. His/her dead body was found lying on the street. At least 1 fatality. ---- Property destruction: On 25 March 2024, in Carrefour - Fontamara Est, Ouest, gang members set fire to the Freres Nau Mixed School. ---- Property destruction: On 27 March 2024, in Port-au-Prince - Canape-Vert, Ouest, the Viv Ansanm Gang set fire to the Superior Normal School (ENS) facilities. It is known that the building was unoccupied when the attack took place. ---- On 1 April 2024, in Port-au-Prince - Champs de Mars, Ouest, police and military forces clashed with the Base 5 Secondes Gang near the National Palace. During clashes, the gang members set fire to a police armored vehicle on the Monseigneur Guilloux street, injuring at least four officers who were inside. Scores of civilians got trapped amidst the crossfire. A person whose body was found on the street with gunshot wounds was likely to have been killed in the crossfire. The armed gangsters looted and robbed the National Library (Centre-Ville neighbourhood). They also entered the Saint-Martial Minor Seminary School (Poste Marchand), burned several vehicles and destroyed some materials, although no casualties among the present colleagues were mentioned. Gunshots were heard on Lamarre street, and on Capois street, as well as in Christ-Roi coming from Nazon. The gang members were described as affiliates of the Living Together gang-led coalition led by the G-9 Gang. At least 1 fatality, at least 4 injured. ---- On 2 April 2024, in Port-au-Prince - Champs de Mars, Ouest, police forces clashed with gang members in the vicinity of the National Palace as these ones opened fire on the institution. A number of gangsters entered the premises of the Haiti State University Hospital (HUEH) (a.k.a. Port-au-Prince General Hospital) and shot at the officers from the hospital's facilities. Smoke rose from the Finance Ministry building. Police forces fired tear gas to disperse the scores of civilians who were nearby. During clashes, a moto taxi driver was shot and killed by a stray bullet in front of the Blaise Pascal School, in Bois Verna neighbourhood (coded separately). Gunshots were also heard in Christ-Roi. The gang members were described as affiliates of the Living Together gang-led coalition (Viv Ansanm gang). No casualties. ---- On 2 April 2024, in Port-au-Prince - Bois Verna, Ouest, police forces clashed with gang members and a man was shot and killed by a stray bullet in front of the Blaise Pascal School. The victim was a moto taxi driver. Gunshots were also heard in Christ-Roi. The gang members were described as affiliates of the Living Together gang-led coalition (Viv Ansanm gang). Clashes also took place in Champs de Mars neighborhood (coded separately). 1 fatality. ---- On 8 April 2024, in Port-au-Prince - Champs de Mars, Ouest, police forces clashed with gang members in the vicinity of the National Palace as the gangsters attacked civilian facilities in the area and around, including the Bird School on the Enterrement street, in Centre Ville neighbourhood (coded separately). Material damages were mentioned at the school. Police forces used megaphones to inform citizens to leave the area. Gunshots were heard throughout the day in Nazon and Lalue neighborhoods, as well as in other areas such as Alerte street, Sylvio Cator Stadium (Morne a Tuf neighborhood), Marche Salomon (Bas Peu de Choses neighborhood), Bolosse Avenue. Casualties unknown. ---- On 8 April 2024, in Port-au-Prince - Centre Ville, Ouest, gang members attacked civilian facilities in the area and around, including the Bird School on the Enterrement street. Material damages were mentioned at the school. Police forces used megaphones to inform citizens to leave the area. Because of that, police forces clashed with gang members in the vicinity of the National Palace in the Champs de Mars neighbourhood (coded separately). Gunshots were heard throughout the day in Nazon and Lalue neighborhoods, as well as in other areas such as Alerte street, Sylvio Cator Stadium (Morne a Tuf neighborhood), Marche Salomon (Bas Peu de Choses neighborhood), Bolosse Avenue. Casualties unknown. ---- Property destruction: Around 11 April 2024 (week of), in Port-au-Prince - Cathedrale, Ouest, armed group members looted and set fire to the JB Damier Vocational School. Some items were stolen. ---- On 23 April 2024, in Port-au-Prince - Bas Peu de Choses, Ouest, in the morning, an unknown number of armed individuals attacked the head of the Jean-Jacques Dessalines high school on the Christophe Avenue (in Bas Peu de Choses neighbourhood). The victim was injured to the head (nature of the wounds unspecified). The motivation for the attack is unknown. 1 injured. ---- Around 29 April 2024 (week of), in Port-au-Prince - Centre Ville, Ouest, armed gang members attacked the Foyer Saint-Vincent facilities (a.k.a. Saint Vicent School for Disabled Children), located on the Paul VI street, in Centre Ville neighbourhood. An unknown number of disabled people (mostly children) were forced to flee the building. Casualties unknown. ---- On 8 May 2024, in Port-au-Prince - Bois Verna, Ouest, in the morning, armed gang members shot and killed a police officer woman as she tried to resist a kidnapping attempt, on the Camille Leon Street (in Bois Verna neighbourhood). The attack took place moments after the officer had left her girl at school (likely off-duty). The attackers stole the officer's firearm and fled the scene on a motorcycle. 1 fatality. ---- On 10 May 2024, in Gressier - Cite Gressier, Ouest, overnight, armed members of the Grand-Ravine Gang set fire to the Gressier police station (Cite Gressier neighbourhood). A police vehicle, the houses of an assessor mayor, and a police, as well as a school building were also burned. Police forces intervened and clashed with the gang members in the vicinity of the police station, although they were unable to expel the criminals, who took control of the facility. A police officer was shot and injured. A public transport driver and several civilians were wounded by the bullets. In Bo Lanme area, a 53-year-old woman was killed in front of her two minor daughters at her home. The girls were later raped by the gang members. In Colombier 9 area, gang members looted a property and stole some items. Members of the Bout Ba Gang also participated in the clashes near the Gressier market, and a man was shot and killed as he received a gunshot to the head. Thousands of residents fled their homes to take refuge elsewhere. The gang members are part of the Living Together gang-led initiative. During the offensive, which last until 11 May, several of them were recorded expressing their rejection to the Multilateral Support Security Mission (MMSS). On 12 May, police forces, supported by the Miragoane police commissioner, and BSAP agents, regained control of the police station after the gang members had abandoned it. At least 2 fatalities, at least 2 injured. ---- On 29 May 2024, in Port-au-Prince - Bas Peu de Choses, Ouest, in the morning, armed gang members on a motorcycle shot and killed a teacher man and head of the School 'Sisters Saint Mary of the Angels' on the Capois street, where the institution is located (Bas Peu de Choses neighbourhood) (drive-by). The victim was said to be driving next to the school when he got shot and lost the control of the vehicle, crashing with a house. According to several sources, the shooting happened as the victim tried to resist a kidnapping attempt. The perpetrators fled the scene. 1 fatality. ---- On 10 June 2024, in Port-au-Prince - Delmas, Ouest, in the morning, the leader of the G-9 Gang launched an attack and set fire to several houses and schools in the commune. Casualties unknown. ---- On 4 July 2024, in Delmas - Delmas 48, Ouest, intern students from the ENS School held a sit-in protest in front of the Ministry of National Education and Vocational Training (MENFP), in Delmas 48 neighbourhood, to demand the payment of their internships. ---- On 22 July 2024, in Gressier, Ouest, armed gang members kidnapped a man at his home and asked for the payment of a ransom to his family as a condition for his release. The victim, who was a public worker at the National Equipment Centre (CNE) and a math's teacher, was not liberated despite the payment of the ransom. The victim's family claimed to have been attacked by the gang members as they contacted the police for help (coded separately). The victim's whereabouts are unknown. ---- On 11 October 2024, in Port-au-Prince - Turgeau, Ouest, an unknown number of people were kidnapped near a school. Although there is no information on the circumstances or perpetrators, latest reports suggest that most abductions are gang-related. Another report indicates that the kidnapping attempt might have been stopped by the police. The victims' whereabouts are unknown. ---- On 8 November 2024, in Delmas - Puits Blain, Ouest, an unknown number of individuals kidnapped two schoolchildren as they were on their way to the school centre. Their whereabouts are unknown. There is no information on the perpetrators and circumstances of the abduction, but the latest reports suggest that most abductions are gang-related. ---- Other: On 1 December 2024, in Port-au-Prince, Ouest, gunshots were heard on Charles Sumner Avenue and near the Sacre Coeur school (Turgeau neighborhood). There is no information on the circumstances or authorship of the gunshots. ---- On 16 January 2025, in Port-au-Prince - Musseau-Delmas 48, Ouest, a group of teachers held a sit-in protest in front of the Ministry of National Education and Vocational Training (MENFP), in Musseau-Delmas 48 neighborhood, demanding better working conditions. The mobilization was part of a teachers' labor strike. ---- On 28 January 2025, in the Kenscoff commune, Ouest, gang members attacked residents and set fire to properties in several areas including Krevites (a.k.a. Prevites), Kikwa (a.k.a. Qui-Croit), Nan Pitimi, Chauffard, Sous Rozo, and Grande Source. Only in Kikwa, 10 students from the Baptist Haiti Mission and two women (described as wives of employees at the mission) were killed as the gangs took over a church and a school, turning them into a gang headquarters. A woman living with physical deficiency was also killed. Between Krevites and Kikwa areas, a pastor from the Christian Brotherhood Union Church and seven family members were killed. This was part of a coordinated armed offensive by the Base 5 Secondes Gang, the Grand-Ravine Gang, and the Ti Bwa Gang (affiliates of the Viv Ansanm Gang) against the Kenscoff commune (coded separately). A report clarified that the offensive was linked to a plan led by the Didi Gang to take control of the close Petionville commune. Between 26 and 30 January, at least 127 civilians had been killed by gangs in Kenscoff and Petionville during the attacks of the Viv Ansanm Gang (up to 150 according to some sources though most of these fatalities remain unconfirmed). At least 127 fatalities split across 26 events. 21 fatalities coded for this event. ---- On 11 February 2025, in Port-au-Prince - Bourdon, Ouest, police forces engaged in armed clashes with gang members. A male student who was on this way to the Centre for Diplomatic and International Studies (CEDI), in Bourdon, was shot and killed by a stray bullet. 1 fatality. ---- On 11 February 2025, in Delmas - St Louis de Gonzague- Henfrasa -Palais de l'art, Ouest, gunshots were heard. A student at the Saint-Louis de Gonzague school was shot and injured by a stray bullet. This was likely part of gang-related attack, as gang engaged in gunfights with police in several neighborhoods in Port-au-Prince on that day (coded separately). 1 injured. ---- Around 19 February 2025 (between 17 - 21 February), in Port-au-Prince - Champs de Mars, Ouest, students from the Faculty of Medicine and Pharmacy of the State University held a march demanding a new headquarters for the General Hospital for them to continue their studies. ---- On 24 February 2025, in Gressier - La Salle Pte Place, Ouest, police forces shot and killed five gang members during clashes in La Salle Pte Place and Lafferonay areas, close to the Don Bosco Salesians School. Three firearms were seized by the police. Clashes were also registered in nearby La Colline area (Gressier) and Flon (Leogane) (coded separately). 5 fatalities. ---- On 24 February 2025, in Tabarre - Tabarre 27, Ouest, overnight, the Kraze Barye Gang attacked the positions of a self-defense group brigade in Tabarre 27 and 25, prompting clashes with the police, who intervened to expel them. During the offensive, the gangsters set fire to residents' houses. A local morgue held up to 15 bodies, although 22 fatal victims were counted in the end. At least four were identified (two men and a woman whose bodies were found on the streets, and a former high school head and executive of the Ministry of Education man killed and burned at his home). A military officer was shot and injured. One source attributed the attack to the 400 Mawozo Gang, although this was not confirmed by other media. 22 fatalities, 1 injured. ---- On 10 March 2025, in Port-au-Prince - Bas Peu de Choses, Ouest, the Grand-Ravine Gang and the Base 5 Secondes Gang (affiliates of the Viv Ansanm Gang coalition) deployed along the Chavannes street and opened fire on the temporary shelter at a Girl's High School, killing a civilian and injuring two others. The victims were part of a group of displaced residents taking shelter at the mentioned institution. Viv Ansanm Gang members also set fire to buildings along the Capois and Alerte streets, and on the Christophe Avenue, killing and injuring several civilians. At least 1 fatality, at least 2 injured. ---- On 11 March 2025, in Port-au-Prince - Bas Peu de Choses, Ouest, the Grand-Ravine Gang and the Base 5 Secondes Gang (in support of the Viv Ansanm Gang) clashed with police forces in Place Jeremie as the criminals attacked residential areas between Place Jeremie, Jean Jacques Dessalines School, and close areas to the Oloffson hotel. Several residents' houses and vehicles were set on fire on Capois, Romain, Chavannes, and Magloire Ambroise streets. Gunshots were heard at the height of Christophe and N Avenues. Many residents fled their homes to take refuge elsewhere. Casualties unknown. ---- On 13 March 2025, in Gressier - La Salle Pte Place, Ouest, BSAP agents supported by members of the population carrying machetes killed four gang members out of a group of 103 occupying the premises of the Peres Salesians de Don Bosco School, located in la Colline area. The BSAP agents shot and killed a security guard suspected of being collaborating with the criminals. 5 fatalities. ---- On 14 March 2025, in Port-au-Prince - Bas Peu de Choses, Ouest, the Viv Ansanm Gang attacked residents on Marcellin, Cameau, and Capois streets. They looted several buildings, including the Infopac School. Other buildings were set on fire. The criminals fired shots and raped a 16-year-old girl. People fled the area. The French Embassy, on Capois street, closed its doors due to gang-related violence in the area. They also targeted nearby areas of the Avenue Christophe neighborhood (coded separately). Casualties unknown. ---- On 19 March 2025, in Port-au-Prince - STEP/Eglise Baptiste de Bolosse, Ouest, the police dropped explosive drones over the territories of several gangs near the Maranatha Evangelical School. This action was also carried out in the downtown area, near Fort-Mercredi, Martissant, Grand Ravine, as well as Delmas 30 neighborhoods (coded separately). In March, police drone airstrike and armed clashes were drones were used resulted in at least 115 gang members killed and 119 injured. At least 115 fatalities split across 19 events. 6 coded here. ---- Other: On 26 March 2025, in Petionville, Ouest, a roadblock of tires was set up on the road near the Union School (Juvenat neighborhood), where the presence of the police was registered. Another roadblock was also registered in Thomassin 32. There is no information on the circumstances or motives of the roadblocks. ---- Other: On 14 Ap</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>26 April 2025 ---- 14 April 2025 ---- 26 March 2025 ---- 19 March 2025 ---- 14 March 2025 ---- 13 March 2025 ---- 11 March 2025 ---- 10 March 2025 ---- 24 February 2025 ---- 24 February 2025 ---- 19 February 2025 ---- 11 February 2025 ---- 11 February 2025 ---- 28 January 2025 ---- 16 January 2025 ---- 01 December 2024 ---- 08 November 2024 ---- 11 October 2024 ---- 22 July 2024 ---- 04 July 2024 ---- 10 June 2024 ---- 29 May 2024 ---- 10 May 2024 ---- 08 May 2024 ---- 29 April 2024 ---- 23 April 2024 ---- 11 April 2024 ---- 08 April 2024 ---- 08 April 2024 ---- 02 April 2024 ---- 02 April 2024 ---- 01 April 2024 ---- 27 March 2024 ---- 25 March 2024 ---- 25 March 2024 ---- 18 March 2024 ---- 18 March 2024 ---- 18 March 2024 ---- 18 March 2024 ---- 08 March 2024 ---- 29 February 2024 ---- 29 February 2024 ---- 29 February 2024 ---- 29 February 2024 ---- 23 February 2024 ---- 23 February 2024 ---- 23 February 2024 ---- 23 February 2024 ---- 17 February 2024 ---- 05 February 2024 ---- 31 January 2024 ---- 30 January 2024 ---- 30 January 2024 ---- 29 January 2024 ---- 28 January 2024 ---- 26 January 2024 ---- 19 January 2024 ---- 09 January 2024</t>
-        </is>
-      </c>
-      <c r="BK2" t="n">
+          <t>2024-01-09 ---- 2024-01-19 ---- 2024-01-26 ---- 2024-01-28 ---- 2024-01-29 ---- 2024-01-30 ---- 2024-01-30 ---- 2024-01-31 ---- 2024-02-05 ---- 2024-02-17 ---- 2024-02-23 ---- 2024-02-23 ---- 2024-02-23 ---- 2024-02-23 ---- 2024-02-29 ---- 2024-02-29 ---- 2024-02-29 ---- 2024-02-29 ---- 2024-03-08 ---- 2024-03-18 ---- 2024-03-18 ---- 2024-03-18 ---- 2024-03-18 ---- 2024-03-25 ---- 2024-03-25 ---- 2024-03-27 ---- 2024-04-01 ---- 2024-04-02 ---- 2024-04-02 ---- 2024-04-08 ---- 2024-04-08 ---- 2024-04-11 ---- 2024-04-23 ---- 2024-04-29 ---- 2024-05-08 ---- 2024-05-10 ---- 2024-05-29 ---- 2024-06-10 ---- 2024-07-04 ---- 2024-07-22 ---- 2024-10-11 ---- 2024-11-08 ---- 2024-12-01 ---- 2025-01-16 ---- 2025-01-28 ---- 2025-02-11 ---- 2025-02-11 ---- 2025-02-19 ---- 2025-02-24 ---- 2025-02-24 ---- 2025-03-10 ---- 2025-03-11 ---- 2025-03-13 ---- 2025-03-14 ---- 2025-03-19 ---- 2025-03-26 ---- 2025-04-14 ---- 2025-04-26 ---- 2025-05-10 ---- 2025-05-26 ---- 2025-06-04</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>Port-au-Prince</t>
+        </is>
+      </c>
+      <c r="BL2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1003,7 +1013,8 @@
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr"/>
       <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="n">
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1024,7 +1035,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1112,7 +1123,8 @@
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="n">
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1133,7 +1145,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1182,22 +1194,22 @@
         <v>12.35</v>
       </c>
       <c r="W5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="X5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
         <v>4</v>
       </c>
       <c r="AA5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AB5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC5" t="n">
         <v>1</v>
@@ -1230,16 +1242,16 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2025-03-10 ---- 2025-02-25 ---- 2025-02-11 ---- 2025-02-11 ---- 2025-02-05 ---- 2024-12-13 ---- 2024-11-08 ---- 2024-08-02 ---- 2024-07-07 ---- 2024-05-23 ---- 2024-04-20 ---- 2024-04-06 ---- 2024-04-03 ---- 2024-04-01 ---- 2024-03-28 ---- 2024-03-26 ---- 2024-03-25 ---- 2024-03-09 ---- 2024-03-04 ---- 2024-02-29 ---- 2024-02-23 ---- 2024-02-19 ---- 2024-01-31 ---- 2024-01-30 ---- 2024-01-23 ---- 2024-01-19</t>
+          <t>2025-05-26 ---- 2025-04-30 ---- 2025-03-18 ---- 2025-03-13 ---- 2025-03-10 ---- 2025-02-25 ---- 2025-02-11 ---- 2025-02-11 ---- 2025-02-05 ---- 2024-12-13 ---- 2024-11-08 ---- 2024-08-02 ---- 2024-07-07 ---- 2024-05-23 ---- 2024-04-20 ---- 2024-04-06 ---- 2024-04-03 ---- 2024-04-01 ---- 2024-03-28 ---- 2024-03-26 ---- 2024-03-25 ---- 2024-03-09 ---- 2024-03-04 ---- 2024-02-29 ---- 2024-02-23 ---- 2024-02-19 ---- 2024-01-31 ---- 2024-01-30 ---- 2024-01-23 ---- 2024-01-19</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>March 2025: A school sheltering IDPs was fired at by the Grand-Ravine Gang and the Base 5 Secondes Gang, killing one person and injuring two others.  ---- February 2025: An education facility was set on fire by armed bandits, trapping students and teachers who were locked inside. ---- February 2025: A student was killed by a stray bullet while he was in a classroom. ---- February 2025: A student at an education facility was injured in the arm by a stray bullet. ---- February 2025: An educator was shot and killed by armed bandits next to an education facility on his way to work. ---- December 2024: An educational facility was set on fire by an unidentified armed gang. ---- November 2024: Two school children were kidnapped by unidentified perpetrators while they were on their way to school.  ---- August 2024: A specialised school was looted and vandalised by 400 Mawozo gang members.  ---- July 2024: A university was raided by an unspecified gang. A number of items were stolen and a church inside the compound was set on fire. ---- May 2024: A university department was looted and damaged by armed perpetrators._x000D_
+          <t>May 2025: An education facility was besieged and four women raped by armed gangs affiliated with the Viv Ansanm coalition. ---- April 2025: The premises of an education facility were reportedly used as a base and regularly occupied by individuals allegedly affiliated with Viv Ansanm gang. ---- March 2025: An education facility was attacked and vandalised by armed individuals. ---- March 2025: An education facility attacked by Viv Ansanm gang members. The facility closed until further notice. ---- March 2025: A school sheltering IDPs was fired at by the Grand-Ravine Gang and the Base 5 Secondes Gang, killing one person and injuring two others.  ---- February 2025: An education facility was set on fire by armed bandits, trapping students and teachers who were locked inside. ---- February 2025: A student was killed by a stray bullet while he was in a classroom. ---- February 2025: A student at an education facility was injured in the arm by a stray bullet. ---- February 2025: An educator was shot and killed by armed bandits next to an education facility on his way to work. ---- December 2024: An educational facility was set on fire by an unidentified armed gang. ---- November 2024: Two school children were kidnapped by unidentified perpetrators while they were on their way to school.  ---- August 2024: A specialised school was looted and vandalised by 400 Mawozo gang members.  ---- July 2024: A university was raided by an unspecified gang. A number of items were stolen and a church inside the compound was set on fire. ---- May 2024: A university department was looted and damaged by armed perpetrators._x000D_
  ---- April 2024: A university faculty was looted and vandalised by armed bandits.  ---- April 2024: A public vocational school was vandalised by armed bandits and equipment looted. ---- April 2024: A library was stormed, looted, and its generator destroyed by armed individuals.  ---- April 2024: A college was attacked, looted and partially burned by armed individuals. Five days later, the direction of the college suspended until further notice all educational activities, whether in person or online. ---- March 2024: A university department was vandalised and set on fire by armed bandits.  ---- March 2024: A school was attacked and set on fire by armed bandits._x000D_
  ---- March 2024: A university department was looted and vandalised by armed bandits._x000D_
  ---- March 2024: A university department was attacked and looted during the night by unidentified perpetrators. Windows, televisions, solar panels were broken, and educational and research laboratory equipment stolen.  ---- March 2024: Several schools were vandalised by armed bandits.  ---- February 2024: University building was stormed by armed individuals. A student was reportedly hit by bullets. ---- February 2024: six catholic brothers and a educator were kidnapped by armed individuals while they were on their way to a mission at a school. The activities of the institution are suspended until further notice.  ---- February 2024: a university professor was kidnapped by armed individuals.  ---- January 2024: School temporarily suspended in-person classes after a stray bullet struck a classroom, opting for remote teaching to ensure student and staff safety.  ---- January 2024: educator assaulted by members of 400 Mawozo gang while on his way to work, resulting in the loss of both his eyes.  ---- January 2024: University campus was invaded by armed individuals from Ti Bwa. Security guards were stripped of their weapons, threatened and forbidden from allowing police officers to enter. In response, all academic activities were temporarily suspended. ---- January 2024: A educator was kidnapped by armed individuals who demanded a ransom for their release. In response, schools in the area temporarily suspended academic activities. All victims were released a week later.</t>
@@ -1247,27 +1259,27 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- On Way To or From School ---- Education Building  ---- On Way To or From School ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Public Building ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- On Way To or From School ---- Unspecified Location ---- Education Building  ---- On Way To or From School ---- Education Building  ---- Private Travel</t>
+          <t>Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- On Way To or From School ---- Education Building  ---- On Way To or From School ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Public Building ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- Education Building  ---- On Way To or From School ---- Unspecified Location ---- Education Building  ---- On Way To or From School ---- Education Building  ---- Private Travel</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Criminal ---- Criminal ---- No Information ---- No Information ---- NSA ---- NSA ---- No Information ---- Criminal ---- No Information ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- No Information ---- Criminal ---- NSA ---- NSA</t>
+          <t>Criminal ---- Criminal ---- Criminal ---- Criminal ---- Criminal ---- Criminal ---- No Information ---- No Information ---- NSA ---- NSA ---- No Information ---- Criminal ---- No Information ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- NSA ---- No Information ---- Criminal ---- NSA ---- NSA</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>Grand Ravine Gang ---- Unspecified gang (Haiti) ---- No Information ---- No Information ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- No Information ---- 400 Mawozo gang (Haiti) ---- No Information ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- No Information ---- 400 Mawozo gang (Haiti) ---- Unidentified Armed Actor ---- Unidentified Armed Actor</t>
+          <t>Viv Ansanm gang (Haiti) ---- Viv Ansanm gang (Haiti) ---- Unspecified gang (Haiti) ---- Viv Ansanm gang (Haiti) ---- Grand Ravine Gang ---- Unspecified gang (Haiti) ---- No Information ---- No Information ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- No Information ---- 400 Mawozo gang (Haiti) ---- No Information ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- Unidentified Armed Actor ---- No Information ---- 400 Mawozo gang (Haiti) ---- Unidentified Armed Actor ---- Unidentified Armed Actor</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>Firearms ---- Arson ---- Firearms ---- Firearms ---- Firearms ---- Arson ---- Firearms ---- No Information on the Weapon Used ---- Arson ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Arson ---- Arson ---- Arson ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms</t>
+          <t>Firearms ---- Firearms ---- No Information on the Weapon Used ---- No Information on the Weapon Used ---- Firearms ---- Arson ---- Firearms ---- Firearms ---- Firearms ---- Arson ---- Firearms ---- No Information on the Weapon Used ---- Arson ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Arson ---- Arson ---- Arson ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms ---- Firearms</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>Secondary School ---- Pre-School ---- University ---- School: No Further Details ---- Not Applicable ---- School: No Further Details ---- Not Applicable ---- School: No Further Details ---- University ---- School: No Further Details ---- University ---- University ---- Other School Infrastructure ---- University ---- University ---- School: No Further Details ---- University ---- University ---- School: No Further Details ---- University ---- Not Applicable ---- Not Applicable ---- School: No Further Details ---- Not Applicable ---- University ---- Not Applicable</t>
+          <t>Secondary School ---- University ---- Secondary School ---- University ---- Secondary School ---- Pre-School ---- University ---- School: No Further Details ---- Not Applicable ---- School: No Further Details ---- Not Applicable ---- School: No Further Details ---- University ---- School: No Further Details ---- University ---- University ---- Other School Infrastructure ---- University ---- University ---- School: No Further Details ---- University ---- University ---- School: No Further Details ---- University ---- Not Applicable ---- Not Applicable ---- School: No Further Details ---- Not Applicable ---- University ---- Not Applicable</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -1294,7 +1306,8 @@
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr"/>
       <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="n">
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1395,7 +1408,8 @@
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr"/>
       <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="n">
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1558,7 +1572,8 @@
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr"/>
       <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="n">
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1579,7 +1594,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1667,7 +1682,8 @@
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr"/>
       <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="n">
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1688,7 +1704,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1776,7 +1792,8 @@
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr"/>
       <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="n">
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1797,7 +1814,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1885,7 +1902,8 @@
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr"/>
       <c r="BJ10" t="inlineStr"/>
-      <c r="BK10" t="n">
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1906,7 +1924,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HT0122;HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0712;HT0721;HT0741;HT0914</t>
+          <t>HT0122;HT0442;HT0712</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1994,7 +2012,8 @@
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr"/>
       <c r="BJ11" t="inlineStr"/>
-      <c r="BK11" t="n">
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2015,7 +2034,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2103,7 +2122,8 @@
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr"/>
       <c r="BJ12" t="inlineStr"/>
-      <c r="BK12" t="n">
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2124,7 +2144,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2266,16 +2286,16 @@
           <t>Ouest</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Croix Des Bouquets</t>
-        </is>
+      <c r="AY13" t="n">
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
         <v>2</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>HT01</t>
+        </is>
       </c>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr">
@@ -2285,12 +2305,12 @@
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>Looting/property destruction ---- Other</t>
+          <t>Other ---- Looting/property destruction</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>Unidentified Gang (Haiti) ---- 400 Mawozo Gang</t>
+          <t>400 Mawozo Gang ---- Unidentified Gang (Haiti)</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr"/>
@@ -2302,15 +2322,20 @@
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Looting: On 2 August 2024, in Croix-des-Bouquets, Ouest, overnight, more than 40 gang members assaulted and occupied the Montfort Institute, a school for deaf-mute and deaf-blind children, located in Duval 30. The attack took place as more than 50 children with special needs were at the facility. The criminals disarmed the security guards, looted the building, stole vehicles and other items, and caused material damages. There were no civilian casualties. The children were evacuated and the occupation persisted at least until 5 August. There were no casualties. ---- Non-violent activity: On 25 June 2024, in Croix-des-Bouquets, Ouest, members of the 400 Mawozo Gang, tried without success to dig the foundations to create a wall along the National Road 8 (at the height of the National High School) in the aim of cutting communication between Croix-des-Bouquets and Tabarre communes. On 4 September, the gang members managed to erect the wall in the mentioned area, commonly known as 'Gran Rigol' area. Police forces demolished it during an intervention on 6 September (coded separately).</t>
+          <t>Non-violent activity: On 25 June 2024, in Croix-des-Bouquets, Ouest, members of the 400 Mawozo Gang, tried without success to dig the foundations to create a wall along the National Road 8 (at the height of the National High School) in the aim of cutting communication between Croix-des-Bouquets and Tabarre communes. On 4 September, the gang members managed to erect the wall in the mentioned area, commonly known as 'Gran Rigol' area. Police forces demolished it during an intervention on 6 September (coded separately). ---- Looting: On 2 August 2024, in Croix-des-Bouquets, Ouest, overnight, more than 40 gang members assaulted and occupied the Montfort Institute, a school for deaf-mute and deaf-blind children, located in Duval 30. The attack took place as more than 50 children with special needs were at the facility. The criminals disarmed the security guards, looted the building, stole vehicles and other items, and caused material damages. There were no civilian casualties. The children were evacuated and the occupation persisted at least until 5 August. There were no casualties.</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>02 August 2024 ---- 25 June 2024</t>
-        </is>
-      </c>
-      <c r="BK13" t="n">
+          <t>2024-06-25 ---- 2024-08-02</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>Croix Des Bouquets</t>
+        </is>
+      </c>
+      <c r="BL13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2411,7 +2436,8 @@
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr"/>
       <c r="BJ14" t="inlineStr"/>
-      <c r="BK14" t="n">
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2512,7 +2538,8 @@
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr"/>
       <c r="BJ15" t="inlineStr"/>
-      <c r="BK15" t="n">
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2613,7 +2640,8 @@
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr"/>
       <c r="BJ16" t="inlineStr"/>
-      <c r="BK16" t="n">
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2634,7 +2662,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HT0135;HT0151;HT0152;HT0214;HT0332;HT0713;HT0715;HT0723;HT0733;HT1021;HT1022</t>
+          <t>HT0135;HT0214;HT0413;HT0713;HT1012</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2722,7 +2750,8 @@
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr"/>
       <c r="BJ17" t="inlineStr"/>
-      <c r="BK17" t="n">
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2823,7 +2852,8 @@
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr"/>
       <c r="BJ18" t="inlineStr"/>
-      <c r="BK18" t="n">
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2924,7 +2954,8 @@
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr"/>
       <c r="BJ19" t="inlineStr"/>
-      <c r="BK19" t="n">
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2945,7 +2976,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HT0135;HT0151;HT0152;HT0214;HT0332;HT0713;HT0715;HT0723;HT0733;HT1021;HT1022</t>
+          <t>HT0151;HT0152;HT0332;HT0715;HT0723;HT0733;HT1021;HT1022</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3033,7 +3064,8 @@
       <c r="BH20" t="inlineStr"/>
       <c r="BI20" t="inlineStr"/>
       <c r="BJ20" t="inlineStr"/>
-      <c r="BK20" t="n">
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3054,7 +3086,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>HT0135;HT0151;HT0152;HT0214;HT0332;HT0713;HT0715;HT0723;HT0733;HT1021;HT1022</t>
+          <t>HT0151;HT0152;HT0332;HT0715;HT0723;HT0733;HT1021;HT1022</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3142,7 +3174,8 @@
       <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="inlineStr"/>
       <c r="BJ21" t="inlineStr"/>
-      <c r="BK21" t="n">
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3163,7 +3196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3243,59 +3276,64 @@
           <t>Sud-Est</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>Jacmel</t>
-        </is>
+      <c r="AY22" t="n">
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>HT02</t>
+        </is>
       </c>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>Riots ---- Protests ---- Protests</t>
+          <t>Protests ---- Protests ---- Riots ---- Violence against civilians ---- Protests</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>Violent demonstration ---- Peaceful protest ---- Peaceful protest</t>
+          <t>Peaceful protest ---- Peaceful protest ---- Violent demonstration ---- Attack ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>Rioters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti)</t>
+          <t>Protesters (Haiti) ---- Protesters (Haiti) ---- Rioters (Haiti) ---- Police Forces of Haiti (2024-) Protected Areas Security Brigade (BSAP) ---- Protesters (Haiti)</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>Students (Haiti) ---- Students (Haiti) ---- Students (Haiti)</t>
+          <t>Students (Haiti) ---- Students (Haiti) ---- Students (Haiti) ---- Labor Group (Haiti)</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>Civilians (Haiti)</t>
+          <t>Civilians (Haiti) ---- Civilians (Haiti)</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>Students (Haiti)</t>
+          <t>Students (Haiti) ---- Taxi/Bus Drivers (Haiti)</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>On 28 January 2025, in Jacmel, Sud-Est, students from the Pinchinat high school took to the streets demanding the return of teachers to classrooms after they went on a labor strike. During the mobilization, demonstrating students threw stones and bottles against the Celie Lamour and the Nossirhel Lherisson schools to press students joining the demonstration. ---- On 15 January 2025, in Jacmel, Sud-Est, hundreds of students from the Jacob Martin Henriquez, Pinchinat, and Celie Lamour high schools took to the streets demanding the return of teachers to classrooms after they went on a labor strike. ---- Around 8 February 2024 (week of), in Jacmel, Sud-Est, a group of students held a protest demanding the presence of teachers at schools.</t>
+          <t>Around 8 February 2024 (week of), in Jacmel, Sud-Est, a group of students held a protest demanding the presence of teachers at schools. ---- On 15 January 2025, in Jacmel, Sud-Est, hundreds of students from the Jacob Martin Henriquez, Pinchinat, and Celie Lamour high schools took to the streets demanding the return of teachers to classrooms after they went on a labor strike. ---- On 28 January 2025, in Jacmel, Sud-Est, students from the Pinchinat high school took to the streets demanding the return of teachers to classrooms after they went on a labor strike. During the mobilization, demonstrating students threw stones and bottles against the Celie Lamour and the Nossirhel Lherisson schools to press students joining the demonstration. ---- On 16 May 2025, in Cayes-Jacmel, Sud-Est, a BSAP police agent opened fire during a traffic altercation with a motorcyclist who tried to cross through an area the officers were securing for a school parade, in the Raymond-les-Bains neighborhood. Eight people, including moto-taxi drivers, parents, and residents, were shot and injured. Four BSAP agents were injured during the altercation (nature of injuries unclarified). The BSAP coordinator claimed that the assigned BSAP officers were not armed and that it was another backup officer who opened fire into the air to disperse people. He also highlighted that some residents were armed, although he did not confirmed whether they used the mentioned arms (of unknown nature) against the officers. A BSAP agent was arrested in connection with the incident. 12 injured. ---- On 9 June 2025, in Jacmel, Sud-Est, contractor workers at the National School Canteen Program (PNCS) protested by closing the institution's offices to demand the payment of nine months of due salary.</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>28 January 2025 ---- 15 January 2025 ---- 08 February 2024</t>
-        </is>
-      </c>
-      <c r="BK22" t="n">
+          <t>2024-02-08 ---- 2025-01-15 ---- 2025-01-28 ---- 2025-05-16 ---- 2025-06-09</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>Jacmel</t>
+        </is>
+      </c>
+      <c r="BL22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3316,7 +3354,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3404,7 +3442,8 @@
       <c r="BH23" t="inlineStr"/>
       <c r="BI23" t="inlineStr"/>
       <c r="BJ23" t="inlineStr"/>
-      <c r="BK23" t="n">
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3425,7 +3464,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3513,7 +3552,8 @@
       <c r="BH24" t="inlineStr"/>
       <c r="BI24" t="inlineStr"/>
       <c r="BJ24" t="inlineStr"/>
-      <c r="BK24" t="n">
+      <c r="BK24" t="inlineStr"/>
+      <c r="BL24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3534,7 +3574,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HT0135;HT0151;HT0152;HT0214;HT0332;HT0713;HT0715;HT0723;HT0733;HT1021;HT1022</t>
+          <t>HT0135;HT0214;HT0413;HT0713;HT1012</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3622,7 +3662,8 @@
       <c r="BH25" t="inlineStr"/>
       <c r="BI25" t="inlineStr"/>
       <c r="BJ25" t="inlineStr"/>
-      <c r="BK25" t="n">
+      <c r="BK25" t="inlineStr"/>
+      <c r="BL25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3643,7 +3684,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3731,7 +3772,8 @@
       <c r="BH26" t="inlineStr"/>
       <c r="BI26" t="inlineStr"/>
       <c r="BJ26" t="inlineStr"/>
-      <c r="BK26" t="n">
+      <c r="BK26" t="inlineStr"/>
+      <c r="BL26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3832,7 +3874,8 @@
       <c r="BH27" t="inlineStr"/>
       <c r="BI27" t="inlineStr"/>
       <c r="BJ27" t="inlineStr"/>
-      <c r="BK27" t="n">
+      <c r="BK27" t="inlineStr"/>
+      <c r="BL27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3853,7 +3896,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3941,7 +3984,8 @@
       <c r="BH28" t="inlineStr"/>
       <c r="BI28" t="inlineStr"/>
       <c r="BJ28" t="inlineStr"/>
-      <c r="BK28" t="n">
+      <c r="BK28" t="inlineStr"/>
+      <c r="BL28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3962,7 +4006,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4050,7 +4094,8 @@
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="inlineStr"/>
       <c r="BJ29" t="inlineStr"/>
-      <c r="BK29" t="n">
+      <c r="BK29" t="inlineStr"/>
+      <c r="BL29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4071,7 +4116,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -4159,7 +4204,8 @@
       <c r="BH30" t="inlineStr"/>
       <c r="BI30" t="inlineStr"/>
       <c r="BJ30" t="inlineStr"/>
-      <c r="BK30" t="n">
+      <c r="BK30" t="inlineStr"/>
+      <c r="BL30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4260,7 +4306,8 @@
       <c r="BH31" t="inlineStr"/>
       <c r="BI31" t="inlineStr"/>
       <c r="BJ31" t="inlineStr"/>
-      <c r="BK31" t="n">
+      <c r="BK31" t="inlineStr"/>
+      <c r="BL31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4281,7 +4328,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4356,64 +4403,21 @@
       <c r="AU32" t="inlineStr"/>
       <c r="AV32" t="inlineStr"/>
       <c r="AW32" t="inlineStr"/>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Nord</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Cap Haitien</t>
-        </is>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>6</v>
-      </c>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr"/>
       <c r="BB32" t="inlineStr"/>
-      <c r="BC32" t="inlineStr">
-        <is>
-          <t>Riots ---- Protests ---- Riots ---- Protests ---- Protests ---- Protests</t>
-        </is>
-      </c>
-      <c r="BD32" t="inlineStr">
-        <is>
-          <t>Violent demonstration ---- Peaceful protest ---- Violent demonstration ---- Protest with intervention ---- Peaceful protest ---- Peaceful protest</t>
-        </is>
-      </c>
-      <c r="BE32" t="inlineStr">
-        <is>
-          <t>Rioters (Haiti) ---- Protesters (Haiti) ---- Rioters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti)</t>
-        </is>
-      </c>
-      <c r="BF32" t="inlineStr">
-        <is>
-          <t>PPD: Platfom Pitit Desalin ---- Students (Haiti) ---- Health Workers (Haiti); Students (Haiti) ---- Health Workers (Haiti); Students (Haiti) ---- Students (Haiti) ---- Students (Haiti)</t>
-        </is>
-      </c>
-      <c r="BG32" t="inlineStr">
-        <is>
-          <t>Civilians (Haiti) ---- Civilians (Haiti) ---- Police Forces of Haiti (2024-)</t>
-        </is>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>PPD: Platfom Pitit Desalin ---- Labor Group (Haiti)</t>
-        </is>
-      </c>
-      <c r="BI32" t="inlineStr">
-        <is>
-          <t>Around 5 March 2025 (between 5 - 6 March), in Cap-Haitien, Nord, Platfom Pitit Desalin party militants and supporters smashed plates and chairs, and beat other members of the party with sticks during a demonstration at the Philippe Guerrier national high school to decry decision making within the party by a small group of foreign agents who, according to demonstrators, are absent from the street movements, but reap all the benefits. The mobilization was held during the holding of a party internal meeting, which was interrupted by demonstrators. ---- Around 14 January 2025 (between 13 - 15 January), in Cap-Haitien, Nord, students took to the streets demanding the return of teachers to classrooms after they went on a labor strike. ---- On 9 September 2024, in Cap-Haitien, Nord, graduates and students from the Medical School of the Henri Christophe campus demonstrated at the Justinian University Hospital to demand more specialized positions. Students of the Higher Institute of Medical Technology (ISTMECH) also demanded their integration in the Haiti State University (UEH) after the ISTMECH was reopened by the director which indicated opposition to the integration. The students barricaded doors, held four employees hostage, and kicked out all patients from the hospital until the police intervened (unknown methods) to regain control of the situation. ---- On 2 September 2024, in Limonade, Nord, medical graduates and students from the UEH University held a sit-in protest at the Justinien University Hospital to demand the departure of the head of the health institution, among other claims. Police forces attended the mobilization and dispersed the protesters (methods unknown). ---- On 28 August 2024, in Limonade, Nord, students protested to demand an end to the ongoing insecurity in Gonaives. ---- Around 25 August 2024 (weekend of), in Limonade, Nord, UEH university students from the Henry Campus held a protest to decry precarious conditions affecting their daily university life. Protesters blocked the march to the Prime Minister's team as the caravan of official vehicles tried to cross the area.</t>
-        </is>
-      </c>
-      <c r="BJ32" t="inlineStr">
-        <is>
-          <t>05 March 2025 ---- 14 January 2025 ---- 09 September 2024 ---- 02 September 2024 ---- 28 August 2024 ---- 25 August 2024</t>
-        </is>
-      </c>
-      <c r="BK32" t="n">
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
+      <c r="BG32" t="inlineStr"/>
+      <c r="BH32" t="inlineStr"/>
+      <c r="BI32" t="inlineStr"/>
+      <c r="BJ32" t="inlineStr"/>
+      <c r="BK32" t="inlineStr"/>
+      <c r="BL32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4434,7 +4438,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H33" t="n">
@@ -4522,7 +4526,8 @@
       <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr"/>
       <c r="BJ33" t="inlineStr"/>
-      <c r="BK33" t="n">
+      <c r="BK33" t="inlineStr"/>
+      <c r="BL33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4543,7 +4548,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -4618,20 +4623,69 @@
       <c r="AU34" t="inlineStr"/>
       <c r="AV34" t="inlineStr"/>
       <c r="AW34" t="inlineStr"/>
-      <c r="AX34" t="inlineStr"/>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr"/>
-      <c r="BA34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Nord</t>
+        </is>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>HT03</t>
+        </is>
+      </c>
       <c r="BB34" t="inlineStr"/>
-      <c r="BC34" t="inlineStr"/>
-      <c r="BD34" t="inlineStr"/>
-      <c r="BE34" t="inlineStr"/>
-      <c r="BF34" t="inlineStr"/>
-      <c r="BG34" t="inlineStr"/>
-      <c r="BH34" t="inlineStr"/>
-      <c r="BI34" t="inlineStr"/>
-      <c r="BJ34" t="inlineStr"/>
-      <c r="BK34" t="n">
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>Protests ---- Protests ---- Protests ---- Riots ---- Protests ---- Riots ---- Protests ---- Protests ---- Protests</t>
+        </is>
+      </c>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>Peaceful protest ---- Peaceful protest ---- Protest with intervention ---- Violent demonstration ---- Peaceful protest ---- Violent demonstration ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest</t>
+        </is>
+      </c>
+      <c r="BE34" t="inlineStr">
+        <is>
+          <t>Protesters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti) ---- Rioters (Haiti) ---- Protesters (Haiti) ---- Rioters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti)</t>
+        </is>
+      </c>
+      <c r="BF34" t="inlineStr">
+        <is>
+          <t>Students (Haiti) ---- Students (Haiti) ---- Health Workers (Haiti); Students (Haiti) ---- Health Workers (Haiti); Students (Haiti) ---- Students (Haiti) ---- PPD: Platfom Pitit Desalin ---- Teachers (Haiti); Students (Haiti)</t>
+        </is>
+      </c>
+      <c r="BG34" t="inlineStr">
+        <is>
+          <t>Police Forces of Haiti (2024-) ---- Civilians (Haiti) ---- Civilians (Haiti)</t>
+        </is>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>Labor Group (Haiti) ---- PPD: Platfom Pitit Desalin</t>
+        </is>
+      </c>
+      <c r="BI34" t="inlineStr">
+        <is>
+          <t>Around 25 August 2024 (weekend of), in Limonade, Nord, UEH university students from the Henry Campus held a protest to decry precarious conditions affecting their daily university life. Protesters blocked the march to the Prime Minister's team as the caravan of official vehicles tried to cross the area. ---- On 28 August 2024, in Limonade, Nord, students protested to demand an end to the ongoing insecurity in Gonaives. ---- On 2 September 2024, in Limonade, Nord, medical graduates and students from the UEH University held a sit-in protest at the Justinien University Hospital to demand the departure of the head of the health institution, among other claims. Police forces attended the mobilization and dispersed the protesters (methods unknown). ---- On 9 September 2024, in Cap-Haitien, Nord, graduates and students from the Medical School of the Henri Christophe campus demonstrated at the Justinian University Hospital to demand more specialized positions. Students of the Higher Institute of Medical Technology (ISTMECH) also demanded their integration in the Haiti State University (UEH) after the ISTMECH was reopened by the director which indicated opposition to the integration. The students barricaded doors, held four employees hostage, and kicked out all patients from the hospital until the police intervened (unknown methods) to regain control of the situation. ---- Around 14 January 2025 (between 13 - 15 January), in Cap-Haitien, Nord, students took to the streets demanding the return of teachers to classrooms after they went on a labor strike. ---- Around 5 March 2025 (between 5 - 6 March), in Cap-Haitien, Nord, Platfom Pitit Desalin party militants and supporters smashed plates and chairs, and beat other members of the party with sticks during a demonstration at the Philippe Guerrier national high school to decry decision making within the party by a small group of foreign agents who, according to demonstrators, are absent from the street movements, but reap all the benefits. The mobilization was held during the holding of a party internal meeting, which was interrupted by demonstrators. ---- On 18 May 2025, in Cap-Haitien, Nord, citizens protested against the government by publicly accusing president of the Transitional Presidential Council (CPT) of being incompetent and a thief. During the protest, a police officer slapped a teacher who was taking part in the mobilization. The teacher slapped him in return. Protesters also expressed frustration over the decision of moving the celebration from Arcahaie, the historic birth place of the flag, to Cap-Haitien. The mobilization was held on the occasion of the Flag Day celebration. ---- On 23 May 2025, in Cap-Haitien, Nord, hundreds of teachers and students protested against the assault of a colleague at the hands of the police during a mobilization held on the occasion of the Flag Day, on 18 May (coded separately). The protesters called for a public apology from the officers involved and demanded appropriate disciplinary action. ---- On 20 June 2025, in Quartier Morin, Nord, residents held a protest and blocked the National Road 6 at the height of Carrefour Lamort to decry the demolition of the fence of a public slot meant for a high school, claiming misuse of a court order.</t>
+        </is>
+      </c>
+      <c r="BJ34" t="inlineStr">
+        <is>
+          <t>2024-08-25 ---- 2024-08-28 ---- 2024-09-02 ---- 2024-09-09 ---- 2025-01-14 ---- 2025-03-05 ---- 2025-05-18 ---- 2025-05-23 ---- 2025-06-20</t>
+        </is>
+      </c>
+      <c r="BK34" t="inlineStr">
+        <is>
+          <t>Cap Haitien</t>
+        </is>
+      </c>
+      <c r="BL34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4652,7 +4706,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H35" t="n">
@@ -4740,7 +4794,8 @@
       <c r="BH35" t="inlineStr"/>
       <c r="BI35" t="inlineStr"/>
       <c r="BJ35" t="inlineStr"/>
-      <c r="BK35" t="n">
+      <c r="BK35" t="inlineStr"/>
+      <c r="BL35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4761,7 +4816,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -4849,7 +4904,8 @@
       <c r="BH36" t="inlineStr"/>
       <c r="BI36" t="inlineStr"/>
       <c r="BJ36" t="inlineStr"/>
-      <c r="BK36" t="n">
+      <c r="BK36" t="inlineStr"/>
+      <c r="BL36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4870,7 +4926,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -4918,30 +4974,92 @@
       <c r="V37" t="n">
         <v>0.55</v>
       </c>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="inlineStr"/>
-      <c r="AQ37" t="inlineStr"/>
-      <c r="AR37" t="inlineStr"/>
-      <c r="AS37" t="inlineStr"/>
-      <c r="AT37" t="inlineStr"/>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>May 2025: An educator was physically assaulted by an unspecified number of Tourist Police Officers (POLITOUR) and slapped by one of them during a peaceful protest for better working conditions. Three officers were arrested.</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>Unspecified Location</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>Police</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>Haitian National Police</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>Fist and Foot</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>Not Applicable</t>
+        </is>
+      </c>
       <c r="AU37" t="inlineStr"/>
       <c r="AV37" t="inlineStr"/>
       <c r="AW37" t="inlineStr"/>
@@ -4958,7 +5076,8 @@
       <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr"/>
       <c r="BJ37" t="inlineStr"/>
-      <c r="BK37" t="n">
+      <c r="BK37" t="inlineStr"/>
+      <c r="BL37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4979,7 +5098,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -5067,7 +5186,8 @@
       <c r="BH38" t="inlineStr"/>
       <c r="BI38" t="inlineStr"/>
       <c r="BJ38" t="inlineStr"/>
-      <c r="BK38" t="n">
+      <c r="BK38" t="inlineStr"/>
+      <c r="BL38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5088,7 +5208,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HT0135;HT0151;HT0152;HT0214;HT0332;HT0713;HT0715;HT0723;HT0733;HT1021;HT1022</t>
+          <t>HT0151;HT0152;HT0332;HT0715;HT0723;HT0733;HT1021;HT1022</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -5176,7 +5296,8 @@
       <c r="BH39" t="inlineStr"/>
       <c r="BI39" t="inlineStr"/>
       <c r="BJ39" t="inlineStr"/>
-      <c r="BK39" t="n">
+      <c r="BK39" t="inlineStr"/>
+      <c r="BL39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5197,7 +5318,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -5285,7 +5406,8 @@
       <c r="BH40" t="inlineStr"/>
       <c r="BI40" t="inlineStr"/>
       <c r="BJ40" t="inlineStr"/>
-      <c r="BK40" t="n">
+      <c r="BK40" t="inlineStr"/>
+      <c r="BL40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5306,7 +5428,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HT0122;HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0712;HT0721;HT0741;HT0914</t>
+          <t>HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0721;HT0741;HT0812;HT0914;HT1014</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -5394,7 +5516,8 @@
       <c r="BH41" t="inlineStr"/>
       <c r="BI41" t="inlineStr"/>
       <c r="BJ41" t="inlineStr"/>
-      <c r="BK41" t="n">
+      <c r="BK41" t="inlineStr"/>
+      <c r="BL41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5495,7 +5618,8 @@
       <c r="BH42" t="inlineStr"/>
       <c r="BI42" t="inlineStr"/>
       <c r="BJ42" t="inlineStr"/>
-      <c r="BK42" t="n">
+      <c r="BK42" t="inlineStr"/>
+      <c r="BL42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5516,7 +5640,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -5604,7 +5728,8 @@
       <c r="BH43" t="inlineStr"/>
       <c r="BI43" t="inlineStr"/>
       <c r="BJ43" t="inlineStr"/>
-      <c r="BK43" t="n">
+      <c r="BK43" t="inlineStr"/>
+      <c r="BL43" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5705,7 +5830,8 @@
       <c r="BH44" t="inlineStr"/>
       <c r="BI44" t="inlineStr"/>
       <c r="BJ44" t="inlineStr"/>
-      <c r="BK44" t="n">
+      <c r="BK44" t="inlineStr"/>
+      <c r="BL44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5726,7 +5852,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -5814,7 +5940,8 @@
       <c r="BH45" t="inlineStr"/>
       <c r="BI45" t="inlineStr"/>
       <c r="BJ45" t="inlineStr"/>
-      <c r="BK45" t="n">
+      <c r="BK45" t="inlineStr"/>
+      <c r="BL45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5915,7 +6042,8 @@
       <c r="BH46" t="inlineStr"/>
       <c r="BI46" t="inlineStr"/>
       <c r="BJ46" t="inlineStr"/>
-      <c r="BK46" t="n">
+      <c r="BK46" t="inlineStr"/>
+      <c r="BL46" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5936,7 +6064,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -6024,7 +6152,8 @@
       <c r="BH47" t="inlineStr"/>
       <c r="BI47" t="inlineStr"/>
       <c r="BJ47" t="inlineStr"/>
-      <c r="BK47" t="n">
+      <c r="BK47" t="inlineStr"/>
+      <c r="BL47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6045,7 +6174,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -6133,7 +6262,8 @@
       <c r="BH48" t="inlineStr"/>
       <c r="BI48" t="inlineStr"/>
       <c r="BJ48" t="inlineStr"/>
-      <c r="BK48" t="n">
+      <c r="BK48" t="inlineStr"/>
+      <c r="BL48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6154,7 +6284,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -6308,7 +6438,8 @@
       <c r="BH49" t="inlineStr"/>
       <c r="BI49" t="inlineStr"/>
       <c r="BJ49" t="inlineStr"/>
-      <c r="BK49" t="n">
+      <c r="BK49" t="inlineStr"/>
+      <c r="BL49" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6401,16 +6532,16 @@
           <t>Nord</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Plaisance</t>
-        </is>
+      <c r="AY50" t="n">
+        <v>0</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA50" t="n">
         <v>1</v>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>HT03</t>
+        </is>
       </c>
       <c r="BB50" t="inlineStr"/>
       <c r="BC50" t="inlineStr">
@@ -6442,10 +6573,15 @@
       </c>
       <c r="BJ50" t="inlineStr">
         <is>
-          <t>18 July 2024</t>
-        </is>
-      </c>
-      <c r="BK50" t="n">
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="BK50" t="inlineStr">
+        <is>
+          <t>Plaisance</t>
+        </is>
+      </c>
+      <c r="BL50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6466,7 +6602,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -6546,51 +6682,56 @@
           <t>Nord-Est</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Fort Liberte</t>
-        </is>
+      <c r="AY51" t="n">
+        <v>0</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA51" t="n">
         <v>9</v>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>HT04</t>
+        </is>
       </c>
       <c r="BB51" t="inlineStr"/>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>Protests ---- Protests ---- Riots ---- Protests ---- Protests ---- Protests ---- Protests ---- Riots ---- Riots</t>
+          <t>Riots ---- Riots ---- Protests ---- Protests ---- Protests ---- Protests ---- Riots ---- Protests ---- Protests</t>
         </is>
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Peaceful protest ---- Violent demonstration ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Violent demonstration ---- Violent demonstration</t>
+          <t>Violent demonstration ---- Violent demonstration ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Violent demonstration ---- Peaceful protest ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
-          <t>Protesters (Haiti) ---- Protesters (Haiti) ---- Rioters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti) ---- Rioters (Haiti) ---- Rioters (Haiti)</t>
+          <t>Rioters (Haiti) ---- Rioters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti) ---- Rioters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti)</t>
         </is>
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>Teachers (Haiti) ---- Students (Haiti); Teachers (Haiti) ---- Teachers (Haiti) ---- Teachers (Haiti) ---- Teachers (Haiti) ---- Teachers (Haiti) ---- Students (Haiti)</t>
+          <t>Students (Haiti) ---- Teachers (Haiti) ---- Teachers (Haiti) ---- Teachers (Haiti) ---- Teachers (Haiti) ---- Students (Haiti); Teachers (Haiti) ---- Teachers (Haiti)</t>
         </is>
       </c>
       <c r="BG51" t="inlineStr"/>
       <c r="BH51" t="inlineStr"/>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>On 31 March 2025, in Fort-Liberte, Nord-Est, scores of public school teachers supported by parents held a protest through the streets of Fort-Liberte to demand better working conditions for the educators, including higher wages, among other claims. ---- On 24 March 2025, in Fort-Liberte, Nord-Est, hundreds of teachers and students, called by the Northern Teachers' Coalition, held a protest at the gates of the Paul Eugene Magloire and La Renaissance schools to demand better working conditions. Protesting teachers blocked access to the school centres. This was part of a teachers' labor strike. ---- On 16 January 2025, in Fort-Liberte, Nord-Est, teachers from public schools and several teachers' organizations took to the streets demanding better working conditions. During the mobilization demonstrators set up barricades of burning tires. This was part of a teachers' labor strike. It was the third time that they demonstrated in Fort-Liberte since 13 January (coded separately). ---- Around 15 January 2025 (between 14 - 15 January), in Fort-Liberte, Nord-Est, teachers from public schools and several teachers' organizations took to the streets demanding better working conditions. The mobilization was part of a teachers' labor strike. It was the second time that they protested in Fort-Liberte since 13 January (coded separately). ---- On 13 January 2025, in Fort-Liberte, Nord-Est, teachers from public schools and several teachers' organizations took to the streets demanding better working conditions. The mobilization was part of a teachers' labor strike. ---- On 6 January 2025, in Fort-Liberte, Nord-Est, several scores of teachers held a protest with banners demanding better working conditions, including the payment of due salaries and benefits, among other claims. Protesters closed the doors of the North-East Departmental Directorate of the Ministry of National Education and Vocational Training (DDNE-MENFP). The mobilization was part of a labor strike. ---- On 6 May 2024, in Fort-Liberte, Nord-Est, students from the Nord-Est Public University (UPNEF) held a march demanding the departure of the institution's administrative council members, among other claims. Protesters used chains to block the entrance of the rectorate. ---- On 29 January 2024, in Fort-Liberte, Nord-Est, residents held a demonstration demanding the departure of Prime Minister, Ariel Henry. They set up barricades of burning tires, stones, pieces of bottles, and tree trucks on several highways. Some public institutions were vandalized with graffiti. Commercial and school activities were paralyzed. The demonstration, which was part of anti-government mobilizations called by Guy Philippe (a former police officer, senator, convict, paramilitary leader, and warlord who had called on taking the streets and leading a revolution in Haiti), was held on the first day of nationwide general strike called by organizations from the political opposition (coded separately). ---- On 25 January 2024, in Fort-Liberte, Nord-Est, residents held a demonstration demanding the departure of Prime Minister, Ariel Henry. Demonstrators set up barricades of burning tires in the Sica neighbourhood. Some public schools closed their doors. This was part of anti-government mobilizations called by Guy Philippe (a former police officer, senator, convict, paramilitary leader, and warlord who had called on taking the streets and leading a revolution in Haiti).</t>
+          <t>On 25 January 2024, in Fort-Liberte, Nord-Est, residents held a demonstration demanding the departure of Prime Minister, Ariel Henry. Demonstrators set up barricades of burning tires in the Sica neighbourhood. Some public schools closed their doors. This was part of anti-government mobilizations called by Guy Philippe (a former police officer, senator, convict, paramilitary leader, and warlord who had called on taking the streets and leading a revolution in Haiti). ---- On 29 January 2024, in Fort-Liberte, Nord-Est, residents held a demonstration demanding the departure of Prime Minister, Ariel Henry. They set up barricades of burning tires, stones, pieces of bottles, and tree trucks on several highways. Some public institutions were vandalized with graffiti. Commercial and school activities were paralyzed. The demonstration, which was part of anti-government mobilizations called by Guy Philippe (a former police officer, senator, convict, paramilitary leader, and warlord who had called on taking the streets and leading a revolution in Haiti), was held on the first day of nationwide general strike called by organizations from the political opposition (coded separately). ---- On 6 May 2024, in Fort-Liberte, Nord-Est, students from the Nord-Est Public University (UPNEF) held a march demanding the departure of the institution's administrative council members, among other claims. Protesters used chains to block the entrance of the rectorate. ---- On 6 January 2025, in Fort-Liberte, Nord-Est, several scores of teachers held a protest with banners demanding better working conditions, including the payment of due salaries and benefits, among other claims. Protesters closed the doors of the North-East Departmental Directorate of the Ministry of National Education and Vocational Training (DDNE-MENFP). The mobilization was part of a labor strike. ---- On 13 January 2025, in Fort-Liberte, Nord-Est, teachers from public schools and several teachers' organizations took to the streets demanding better working conditions. The mobilization was part of a teachers' labor strike. ---- Around 15 January 2025 (between 14 - 15 January), in Fort-Liberte, Nord-Est, teachers from public schools and several teachers' organizations took to the streets demanding better working conditions. The mobilization was part of a teachers' labor strike. It was the second time that they protested in Fort-Liberte since 13 January (coded separately). ---- On 16 January 2025, in Fort-Liberte, Nord-Est, teachers from public schools and several teachers' organizations took to the streets demanding better working conditions. During the mobilization demonstrators set up barricades of burning tires. This was part of a teachers' labor strike. It was the third time that they demonstrated in Fort-Liberte since 13 January (coded separately). ---- On 24 March 2025, in Fort-Liberte, Nord-Est, hundreds of teachers and students, called by the Northern Teachers' Coalition, held a protest at the gates of the Paul Eugene Magloire and La Renaissance schools to demand better working conditions. Protesting teachers blocked access to the school centres. This was part of a teachers' labor strike. ---- On 31 March 2025, in Fort-Liberte, Nord-Est, scores of public school teachers supported by parents held a protest through the streets of Fort-Liberte to demand better working conditions for the educators, including higher wages, among other claims.</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr">
         <is>
-          <t>31 March 2025 ---- 24 March 2025 ---- 16 January 2025 ---- 15 January 2025 ---- 13 January 2025 ---- 06 January 2025 ---- 06 May 2024 ---- 29 January 2024 ---- 25 January 2024</t>
-        </is>
-      </c>
-      <c r="BK51" t="n">
+          <t>2024-01-25 ---- 2024-01-29 ---- 2024-05-06 ---- 2025-01-06 ---- 2025-01-13 ---- 2025-01-15 ---- 2025-01-16 ---- 2025-03-24 ---- 2025-03-31</t>
+        </is>
+      </c>
+      <c r="BK51" t="inlineStr">
+        <is>
+          <t>Fort Liberte</t>
+        </is>
+      </c>
+      <c r="BL51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6611,7 +6752,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>HT0122;HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0712;HT0721;HT0741;HT0914</t>
+          <t>HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0721;HT0741;HT0812;HT0914;HT1014</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -6699,7 +6840,8 @@
       <c r="BH52" t="inlineStr"/>
       <c r="BI52" t="inlineStr"/>
       <c r="BJ52" t="inlineStr"/>
-      <c r="BK52" t="n">
+      <c r="BK52" t="inlineStr"/>
+      <c r="BL52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6715,12 +6857,12 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HT0442</t>
+          <t>HT1012</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0135;HT0214;HT0413;HT0713;HT1012</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -6808,7 +6950,8 @@
       <c r="BH53" t="inlineStr"/>
       <c r="BI53" t="inlineStr"/>
       <c r="BJ53" t="inlineStr"/>
-      <c r="BK53" t="n">
+      <c r="BK53" t="inlineStr"/>
+      <c r="BL53" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6829,7 +6972,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -6909,16 +7052,16 @@
           <t>Nord-Est</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Ouanaminthe</t>
-        </is>
+      <c r="AY54" t="n">
+        <v>0</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA54" t="n">
         <v>1</v>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>HT04</t>
+        </is>
       </c>
       <c r="BB54" t="inlineStr"/>
       <c r="BC54" t="inlineStr">
@@ -6950,10 +7093,15 @@
       </c>
       <c r="BJ54" t="inlineStr">
         <is>
-          <t>18 February 2024</t>
-        </is>
-      </c>
-      <c r="BK54" t="n">
+          <t>2024-02-18</t>
+        </is>
+      </c>
+      <c r="BK54" t="inlineStr">
+        <is>
+          <t>Ouanaminthe</t>
+        </is>
+      </c>
+      <c r="BL54" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6974,7 +7122,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>HT0122;HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0712;HT0721;HT0741;HT0914</t>
+          <t>HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0721;HT0741;HT0812;HT0914;HT1014</t>
         </is>
       </c>
       <c r="H55" t="n">
@@ -7124,7 +7272,8 @@
       <c r="BH55" t="inlineStr"/>
       <c r="BI55" t="inlineStr"/>
       <c r="BJ55" t="inlineStr"/>
-      <c r="BK55" t="n">
+      <c r="BK55" t="inlineStr"/>
+      <c r="BL55" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7145,7 +7294,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -7233,7 +7382,8 @@
       <c r="BH56" t="inlineStr"/>
       <c r="BI56" t="inlineStr"/>
       <c r="BJ56" t="inlineStr"/>
-      <c r="BK56" t="n">
+      <c r="BK56" t="inlineStr"/>
+      <c r="BL56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7254,7 +7404,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -7342,7 +7492,8 @@
       <c r="BH57" t="inlineStr"/>
       <c r="BI57" t="inlineStr"/>
       <c r="BJ57" t="inlineStr"/>
-      <c r="BK57" t="n">
+      <c r="BK57" t="inlineStr"/>
+      <c r="BL57" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7363,7 +7514,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -7451,7 +7602,8 @@
       <c r="BH58" t="inlineStr"/>
       <c r="BI58" t="inlineStr"/>
       <c r="BJ58" t="inlineStr"/>
-      <c r="BK58" t="n">
+      <c r="BK58" t="inlineStr"/>
+      <c r="BL58" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7472,7 +7624,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -7552,16 +7704,16 @@
           <t>Nord-Est</t>
         </is>
       </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Trou Du Nord</t>
-        </is>
+      <c r="AY59" t="n">
+        <v>0</v>
       </c>
       <c r="AZ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA59" t="n">
         <v>2</v>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>HT04</t>
+        </is>
       </c>
       <c r="BB59" t="inlineStr"/>
       <c r="BC59" t="inlineStr">
@@ -7589,10 +7741,15 @@
       </c>
       <c r="BJ59" t="inlineStr">
         <is>
-          <t>29 January 2024 ---- 29 January 2024</t>
-        </is>
-      </c>
-      <c r="BK59" t="n">
+          <t>2024-01-29 ---- 2024-01-29</t>
+        </is>
+      </c>
+      <c r="BK59" t="inlineStr">
+        <is>
+          <t>Trou Du Nord</t>
+        </is>
+      </c>
+      <c r="BL59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7613,7 +7770,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H60" t="n">
@@ -7701,7 +7858,8 @@
       <c r="BH60" t="inlineStr"/>
       <c r="BI60" t="inlineStr"/>
       <c r="BJ60" t="inlineStr"/>
-      <c r="BK60" t="n">
+      <c r="BK60" t="inlineStr"/>
+      <c r="BL60" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7722,7 +7880,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -7810,7 +7968,8 @@
       <c r="BH61" t="inlineStr"/>
       <c r="BI61" t="inlineStr"/>
       <c r="BJ61" t="inlineStr"/>
-      <c r="BK61" t="n">
+      <c r="BK61" t="inlineStr"/>
+      <c r="BL61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7826,12 +7985,12 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>HT0421</t>
+          <t>HT0712</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0122;HT0442;HT0712</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -7919,7 +8078,8 @@
       <c r="BH62" t="inlineStr"/>
       <c r="BI62" t="inlineStr"/>
       <c r="BJ62" t="inlineStr"/>
-      <c r="BK62" t="n">
+      <c r="BK62" t="inlineStr"/>
+      <c r="BL62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7940,7 +8100,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -8028,7 +8188,8 @@
       <c r="BH63" t="inlineStr"/>
       <c r="BI63" t="inlineStr"/>
       <c r="BJ63" t="inlineStr"/>
-      <c r="BK63" t="n">
+      <c r="BK63" t="inlineStr"/>
+      <c r="BL63" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8196,36 +8357,36 @@
           <t>Artibonite</t>
         </is>
       </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>Gonaives</t>
-        </is>
+      <c r="AY64" t="n">
+        <v>1</v>
       </c>
       <c r="AZ64" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA64" t="n">
         <v>5</v>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>HT05</t>
+        </is>
       </c>
       <c r="BB64" t="inlineStr"/>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>Protests ---- Protests ---- Violence against civilians ---- Violence against civilians ---- Protests</t>
+          <t>Protests ---- Violence against civilians ---- Violence against civilians ---- Protests ---- Protests</t>
         </is>
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Peaceful protest ---- Attack ---- Abduction/forced disappearance ---- Peaceful protest</t>
+          <t>Peaceful protest ---- Abduction/forced disappearance ---- Attack ---- Peaceful protest ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>Protesters (Haiti) ---- Protesters (Haiti) ---- 5 Etoiles Gang ---- Kokorat San Ras Gang ---- Protesters (Haiti)</t>
+          <t>Protesters (Haiti) ---- Kokorat San Ras Gang ---- 5 Etoiles Gang ---- Protesters (Haiti) ---- Protesters (Haiti)</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>Students (Haiti) ---- Teachers (Haiti) ---- Teachers (Haiti)</t>
+          <t>Teachers (Haiti) ---- Teachers (Haiti) ---- Students (Haiti)</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr">
@@ -8240,15 +8401,20 @@
       </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>Around 14 January 2025 (between 13 - 15 January), in Gonaives, Artibonite, students took to the streets demanding the return of teachers to classrooms after they went on a labor strike. ---- On 6 January 2025, in Gonaives, Artibonite, a group of teachers held a sit-in protest in front of the office of the Departmental Directorate of Education demanding better working conditions. The mobilization was part of a labor strike. ---- On 21 October 2024, in L'Estere, Artibonite, members of the 5 Etoiles Gang (a subsidiary and allied gang of the Kokorat San Ras Gang) moving on a motorcycle opened indiscriminate fire against the Congregational Presbyterian School (drive-by) and killed at least a man (parent of a student). One of the sources stated that there could have been at least 10 fatalities among students and civilians who were leaving or near the school's compound, including a parent and the high school janitor. Several students and a 3-year-old boy were injured. At least 1 fatalities, several injured. ---- On 10 October 2024, in Lacroix-Perisse, Artibonite, the Kokorat San Ras Gang kidnapped two men on the National Road 1. The victims were the Saint-Marc School District Office's head inspector, and a messenger man. They were on their way to Gonaives when the abductors intercepted them on the road. Their whereabouts are unknown. ---- On 27 February 2024, in Gonaives, Artibonite, several dozens of teachers held a sit-in protest with banners in front of a police station demanding the return of school classes. Protesters called on police forces to take their responsibility regarding the insecurity situation.</t>
+          <t>On 27 February 2024, in Gonaives, Artibonite, several dozens of teachers held a sit-in protest with banners in front of a police station demanding the return of school classes. Protesters called on police forces to take their responsibility regarding the insecurity situation. ---- On 10 October 2024, in Lacroix-Perisse, Artibonite, the Kokorat San Ras Gang kidnapped two men on the National Road 1. The victims were the Saint-Marc School District Office's head inspector, and a messenger man. They were on their way to Gonaives when the abductors intercepted them on the road. Their whereabouts are unknown. ---- On 21 October 2024, in L'Estere, Artibonite, members of the 5 Etoiles Gang (a subsidiary and allied gang of the Kokorat San Ras Gang) moving on a motorcycle opened indiscriminate fire against the Congregational Presbyterian School (drive-by) and killed at least a man (parent of a student). One of the sources stated that there could have been at least 10 fatalities among students and civilians who were leaving or near the school's compound, including a parent and the high school janitor. Several students and a 3-year-old boy were injured. At least 1 fatalities, several injured. ---- On 6 January 2025, in Gonaives, Artibonite, a group of teachers held a sit-in protest in front of the office of the Departmental Directorate of Education demanding better working conditions. The mobilization was part of a labor strike. ---- Around 14 January 2025 (between 13 - 15 January), in Gonaives, Artibonite, students took to the streets demanding the return of teachers to classrooms after they went on a labor strike.</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr">
         <is>
-          <t>14 January 2025 ---- 06 January 2025 ---- 21 October 2024 ---- 10 October 2024 ---- 27 February 2024</t>
-        </is>
-      </c>
-      <c r="BK64" t="n">
+          <t>2024-02-27 ---- 2024-10-10 ---- 2024-10-21 ---- 2025-01-06 ---- 2025-01-14</t>
+        </is>
+      </c>
+      <c r="BK64" t="inlineStr">
+        <is>
+          <t>Gonaives</t>
+        </is>
+      </c>
+      <c r="BL64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8357,7 +8523,8 @@
       <c r="BH65" t="inlineStr"/>
       <c r="BI65" t="inlineStr"/>
       <c r="BJ65" t="inlineStr"/>
-      <c r="BK65" t="n">
+      <c r="BK65" t="inlineStr"/>
+      <c r="BL65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8458,7 +8625,8 @@
       <c r="BH66" t="inlineStr"/>
       <c r="BI66" t="inlineStr"/>
       <c r="BJ66" t="inlineStr"/>
-      <c r="BK66" t="n">
+      <c r="BK66" t="inlineStr"/>
+      <c r="BL66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8567,7 +8735,8 @@
       <c r="BH67" t="inlineStr"/>
       <c r="BI67" t="inlineStr"/>
       <c r="BJ67" t="inlineStr"/>
-      <c r="BK67" t="n">
+      <c r="BK67" t="inlineStr"/>
+      <c r="BL67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8660,37 +8829,37 @@
           <t>Artibonite</t>
         </is>
       </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>Gros Morne</t>
-        </is>
+      <c r="AY68" t="n">
+        <v>8</v>
       </c>
       <c r="AZ68" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA68" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>HT05</t>
+        </is>
       </c>
       <c r="BB68" t="inlineStr"/>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>Violence against civilians</t>
+          <t>Violence against civilians ---- Violence against civilians</t>
         </is>
       </c>
       <c r="BD68" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Attack ---- Attack</t>
         </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
-          <t>Kokorat San Ras Gang</t>
+          <t>Kokorat San Ras Gang ---- Kokorat San Ras Gang</t>
         </is>
       </c>
       <c r="BF68" t="inlineStr"/>
       <c r="BG68" t="inlineStr">
         <is>
-          <t>Civilians (Haiti)</t>
+          <t>Civilians (Haiti) ---- Civilians (Haiti)</t>
         </is>
       </c>
       <c r="BH68" t="inlineStr">
@@ -8700,15 +8869,20 @@
       </c>
       <c r="BI68" t="inlineStr">
         <is>
-          <t>On 14 June 2024, in Terre Neuve, Artibonite, around 30 members of the Kokorat San Ras Gang riding motorcycles attacked residents in the Lagon communal section, shooting and killing six civilians and injuring a woman. Among the fatal victims, there were an Evangelical pastor from the Bethel Church (also described as head of a school), and two other teachers. The religious man had been kidnapped moments before being killed. The house of a former coordinator of the regional Board of Directors of the Municipal Section (CASEC) was set on fire. After the attack, the gangsters left the commune and killed four other civilians in nearby Grande Plaine (coded separately). These attacks resulted in more than 10 fatalities, at least 15 injured, and around 20 houses burned between Terre Neuve and Grande Plaine. At least 6 fatalities, at least 1 injured.</t>
+          <t>On 14 June 2024, in Terre Neuve, Artibonite, around 30 members of the Kokorat San Ras Gang riding motorcycles attacked residents in the Lagon communal section, shooting and killing six civilians and injuring a woman. Among the fatal victims, there were an Evangelical pastor from the Bethel Church (also described as head of a school), and two other teachers. The religious man had been kidnapped moments before being killed. The house of a former coordinator of the regional Board of Directors of the Municipal Section (CASEC) was set on fire. After the attack, the gangsters left the commune and killed four other civilians in nearby Grande Plaine (coded separately). These attacks resulted in more than 10 fatalities, at least 15 injured, and around 20 houses burned between Terre Neuve and Grande Plaine. At least 6 fatalities, at least 1 injured. ---- On 6 August 2025, in the Gros-Morne commune, Artibonite, members of the Kokorat San Ras Gang carried out an attack, shooting and killing two people, and injuring a third one near the Jacques Roumain school, in the Pay Kann locality. The motivation for the attack is unknown. 2 fatalities. 1 injured.</t>
         </is>
       </c>
       <c r="BJ68" t="inlineStr">
         <is>
-          <t>14 June 2024</t>
-        </is>
-      </c>
-      <c r="BK68" t="n">
+          <t>2024-06-14 ---- 2025-08-06</t>
+        </is>
+      </c>
+      <c r="BK68" t="inlineStr">
+        <is>
+          <t>Gros Morne</t>
+        </is>
+      </c>
+      <c r="BL68" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8817,7 +8991,8 @@
       <c r="BH69" t="inlineStr"/>
       <c r="BI69" t="inlineStr"/>
       <c r="BJ69" t="inlineStr"/>
-      <c r="BK69" t="n">
+      <c r="BK69" t="inlineStr"/>
+      <c r="BL69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8972,31 +9147,31 @@
           <t>Artibonite</t>
         </is>
       </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Saint Marc</t>
-        </is>
+      <c r="AY70" t="n">
+        <v>115</v>
       </c>
       <c r="AZ70" t="n">
-        <v>115</v>
-      </c>
-      <c r="BA70" t="n">
         <v>4</v>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>HT05</t>
+        </is>
       </c>
       <c r="BB70" t="inlineStr"/>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>Protests ---- Protests ---- Protests ---- Violence against civilians</t>
+          <t>Violence against civilians ---- Protests ---- Protests ---- Protests</t>
         </is>
       </c>
       <c r="BD70" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Protest with intervention ---- Peaceful protest ---- Attack</t>
+          <t>Sexual violence ---- Peaceful protest ---- Protest with intervention ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
-          <t>Protesters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti) ---- Baz Gran Grif de Savien Gang</t>
+          <t>Baz Gran Grif de Savien Gang ---- Protesters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti)</t>
         </is>
       </c>
       <c r="BF70" t="inlineStr">
@@ -9006,7 +9181,7 @@
       </c>
       <c r="BG70" t="inlineStr">
         <is>
-          <t>Unidentified Armed Group (Haiti) ---- Civilians (Haiti)</t>
+          <t>Civilians (Haiti) ---- Unidentified Armed Group (Haiti)</t>
         </is>
       </c>
       <c r="BH70" t="inlineStr">
@@ -9016,15 +9191,20 @@
       </c>
       <c r="BI70" t="inlineStr">
         <is>
-          <t>Around 14 January 2025 (between 13 - 15 January), in Saint-Marc, Artibonite, students took to the streets demanding the return of teachers to classrooms after they went on a labor strike. ---- On 23 October 2024, in Saint-Marc, Artibonite, a group of students held a protest at the UPBAS University compound over unspecified claims. During the protest, armed individuals threatened and aggressed the students. A journalist man who was covering the mobilization was aggressed by a faculty dean and former deputy of the Saint-Marc commune. The aggressor lunged at him with a punch. The journalist's equipment (cell phone screen) was damaged. ---- On 14 October 2024, in Saint-Marc, Artibonite, students of the Antoinette Dessalines National School held a march demanding the authorities to address the situation of the displaced people from Pont Sonde who were sheltering at their school after gang attacks of 3 October (coded separately). Protesters blocked the National Road 1 (RN1). ---- On 3 October 2024, in Pont Sonde, Artibonite, in the early morning, dozens of members of the Baz Gran Grif de Savien Gang shot and killed at least 115 civilians (including at least 10 women and three babies), and injured 357 as they occupied the National Road 1 and set fire to residents' properties. Some of the fatal victims were identified as a voodoo priest, a school principal, and several vendors. At least 45 houses and 34 vehicles were burned in La Poterie area. The attack was a reprisal against the Coalition of Revolutionnaires to Save the Artibonite self-defense group for encouraging the local population to use agricultural roads to avoid toll booths installed by the Baz Gran Grif de Savien Gang on the National Road 1 (coded separately). The self-defense group tried to fight back by blocking the bridge into town, but the gang members invaded from the Artibonite River waters. The victims were described as unharmed civilians. More than 6,200 people fled their homes. An unspecified number went missing as they tried to flee. At least 115 fatalities, 357 injured.</t>
+          <t>On 3 October 2024, in Pont Sonde, Artibonite, in the early morning, dozens of members of the Baz Gran Grif de Savien Gang shot and killed at least 115 civilians (including at least 10 women and three babies), and injured 357 as they occupied the National Road 1 and set fire to residents' properties. At least five cases of rape were mentioned, including one involving a minor. Some of the fatal victims were identified as a voodoo priest, a school principal, and several vendors. At least 45 houses and 34 vehicles were burned in La Poterie area. The attack was a reprisal against the Coalition of Revolutionnaires to Save the Artibonite self-defense group for encouraging the local population to use agricultural roads to avoid toll booths installed by the Baz Gran Grif de Savien Gang on the National Road 1 (coded separately). The self-defense group tried to fight back by blocking the bridge into town, but the gang members invaded from the Artibonite River waters. The victims were described as unharmed civilians. More than 6,200 people fled their homes. An unspecified number went missing as they tried to flee. At least 115 fatalities, 357 injured. ---- On 14 October 2024, in Saint-Marc, Artibonite, students of the Antoinette Dessalines National School held a march demanding the authorities to address the situation of the displaced people from Pont Sonde who were sheltering at their school after gang attacks of 3 October (coded separately). Protesters blocked the National Road 1 (RN1). ---- On 23 October 2024, in Saint-Marc, Artibonite, a group of students held a protest at the UPBAS University compound over unspecified claims. During the protest, armed individuals threatened and aggressed the students. A journalist man who was covering the mobilization was aggressed by a faculty dean and former deputy of the Saint-Marc commune. The aggressor lunged at him with a punch. The journalist's equipment (cell phone screen) was damaged. ---- Around 14 January 2025 (between 13 - 15 January), in Saint-Marc, Artibonite, students took to the streets demanding the return of teachers to classrooms after they went on a labor strike.</t>
         </is>
       </c>
       <c r="BJ70" t="inlineStr">
         <is>
-          <t>14 January 2025 ---- 23 October 2024 ---- 14 October 2024 ---- 03 October 2024</t>
-        </is>
-      </c>
-      <c r="BK70" t="n">
+          <t>2024-10-03 ---- 2024-10-14 ---- 2024-10-23 ---- 2025-01-14</t>
+        </is>
+      </c>
+      <c r="BK70" t="inlineStr">
+        <is>
+          <t>Saint Marc</t>
+        </is>
+      </c>
+      <c r="BL70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9133,7 +9313,8 @@
       <c r="BH71" t="inlineStr"/>
       <c r="BI71" t="inlineStr"/>
       <c r="BJ71" t="inlineStr"/>
-      <c r="BK71" t="n">
+      <c r="BK71" t="inlineStr"/>
+      <c r="BL71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9242,7 +9423,8 @@
       <c r="BH72" t="inlineStr"/>
       <c r="BI72" t="inlineStr"/>
       <c r="BJ72" t="inlineStr"/>
-      <c r="BK72" t="n">
+      <c r="BK72" t="inlineStr"/>
+      <c r="BL72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9413,7 +9595,8 @@
       <c r="BH73" t="inlineStr"/>
       <c r="BI73" t="inlineStr"/>
       <c r="BJ73" t="inlineStr"/>
-      <c r="BK73" t="n">
+      <c r="BK73" t="inlineStr"/>
+      <c r="BL73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9506,16 +9689,16 @@
           <t>Artibonite</t>
         </is>
       </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Dessalines</t>
-        </is>
+      <c r="AY74" t="n">
+        <v>35</v>
       </c>
       <c r="AZ74" t="n">
-        <v>35</v>
-      </c>
-      <c r="BA74" t="n">
         <v>1</v>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>HT05</t>
+        </is>
       </c>
       <c r="BB74" t="inlineStr"/>
       <c r="BC74" t="inlineStr">
@@ -9546,15 +9729,20 @@
       <c r="BH74" t="inlineStr"/>
       <c r="BI74" t="inlineStr">
         <is>
-          <t>On 10 December 2024, in Petite Riviere de l'Artibonite, Artibonite, overnight, members of the Palmiste Gang and the Lika Gang in support of the Baz Gran Grif de Savien Gang shot and killed at least nine civilians (including children) at homes near the Henri Christophe School (between Capois Street and the 14eme/Quatorzieme area). 10 houses and three vehicles were burned. On 10 December, gang members killed at least 70 civilians in locations in the Petite Riviere de l'Artibonite commune in reprisal for having helped officers retake control of a police headquarters (coded separately). Several dozen people were kidnapped. Some of them were found executed in nearby properties the day after. The other abducted victims' whereabouts are unknown. At least 70 fatalities split across two events. 35 fatalities coded here.</t>
+          <t>On 10 December 2024, in Petite Riviere de l'Artibonite, Artibonite, overnight, members of the Palmiste Gang and the Lika Gang in support of the Baz Gran Grif de Savien Gang shot and killed at least nine civilians (including children) at homes near the Henri Christophe School (between Capois Street and the 14eme/Quatorzieme area). 10 houses and three vehicles were burned. On 10 December, gang members killed at least 70 civilians (40 men, 20 women, and 10 minors) in locations in the Petite Riviere de l'Artibonite commune in reprisal for having helped officers retake control of a police headquarters (coded separately). 20 people, including 12 men and eight women, were kidnapped during this an another attack recorded in Petite Riviere de L'Artibonite on the same day. Some of them were found executed in nearby properties the day after. The other abducted victims' whereabouts are unknown. At least 70 fatalities split across two events. 35 fatalities coded here.</t>
         </is>
       </c>
       <c r="BJ74" t="inlineStr">
         <is>
-          <t>10 December 2024</t>
-        </is>
-      </c>
-      <c r="BK74" t="n">
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="BK74" t="inlineStr">
+        <is>
+          <t>Dessalines</t>
+        </is>
+      </c>
+      <c r="BL74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9663,7 +9851,8 @@
       <c r="BH75" t="inlineStr"/>
       <c r="BI75" t="inlineStr"/>
       <c r="BJ75" t="inlineStr"/>
-      <c r="BK75" t="n">
+      <c r="BK75" t="inlineStr"/>
+      <c r="BL75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9772,7 +9961,8 @@
       <c r="BH76" t="inlineStr"/>
       <c r="BI76" t="inlineStr"/>
       <c r="BJ76" t="inlineStr"/>
-      <c r="BK76" t="n">
+      <c r="BK76" t="inlineStr"/>
+      <c r="BL76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9881,7 +10071,8 @@
       <c r="BH77" t="inlineStr"/>
       <c r="BI77" t="inlineStr"/>
       <c r="BJ77" t="inlineStr"/>
-      <c r="BK77" t="n">
+      <c r="BK77" t="inlineStr"/>
+      <c r="BL77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9990,7 +10181,8 @@
       <c r="BH78" t="inlineStr"/>
       <c r="BI78" t="inlineStr"/>
       <c r="BJ78" t="inlineStr"/>
-      <c r="BK78" t="n">
+      <c r="BK78" t="inlineStr"/>
+      <c r="BL78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10011,7 +10203,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H79" t="n">
@@ -10099,7 +10291,8 @@
       <c r="BH79" t="inlineStr"/>
       <c r="BI79" t="inlineStr"/>
       <c r="BJ79" t="inlineStr"/>
-      <c r="BK79" t="n">
+      <c r="BK79" t="inlineStr"/>
+      <c r="BL79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10120,7 +10313,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H80" t="n">
@@ -10208,7 +10401,8 @@
       <c r="BH80" t="inlineStr"/>
       <c r="BI80" t="inlineStr"/>
       <c r="BJ80" t="inlineStr"/>
-      <c r="BK80" t="n">
+      <c r="BK80" t="inlineStr"/>
+      <c r="BL80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10229,7 +10423,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>HT0122;HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0712;HT0721;HT0741;HT0914</t>
+          <t>HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0721;HT0741;HT0812;HT0914;HT1014</t>
         </is>
       </c>
       <c r="H81" t="n">
@@ -10317,7 +10511,8 @@
       <c r="BH81" t="inlineStr"/>
       <c r="BI81" t="inlineStr"/>
       <c r="BJ81" t="inlineStr"/>
-      <c r="BK81" t="n">
+      <c r="BK81" t="inlineStr"/>
+      <c r="BL81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10338,7 +10533,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H82" t="n">
@@ -10426,7 +10621,8 @@
       <c r="BH82" t="inlineStr"/>
       <c r="BI82" t="inlineStr"/>
       <c r="BJ82" t="inlineStr"/>
-      <c r="BK82" t="n">
+      <c r="BK82" t="inlineStr"/>
+      <c r="BL82" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10447,7 +10643,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -10495,30 +10691,92 @@
       <c r="V83" t="n">
         <v>2.42</v>
       </c>
-      <c r="W83" t="inlineStr"/>
-      <c r="X83" t="inlineStr"/>
-      <c r="Y83" t="inlineStr"/>
-      <c r="Z83" t="inlineStr"/>
-      <c r="AA83" t="inlineStr"/>
-      <c r="AB83" t="inlineStr"/>
-      <c r="AC83" t="inlineStr"/>
-      <c r="AD83" t="inlineStr"/>
-      <c r="AE83" t="inlineStr"/>
-      <c r="AF83" t="inlineStr"/>
-      <c r="AG83" t="inlineStr"/>
-      <c r="AH83" t="inlineStr"/>
-      <c r="AI83" t="inlineStr"/>
-      <c r="AJ83" t="inlineStr"/>
-      <c r="AK83" t="inlineStr"/>
-      <c r="AL83" t="inlineStr"/>
-      <c r="AM83" t="inlineStr"/>
-      <c r="AN83" t="inlineStr"/>
-      <c r="AO83" t="inlineStr"/>
-      <c r="AP83" t="inlineStr"/>
-      <c r="AQ83" t="inlineStr"/>
-      <c r="AR83" t="inlineStr"/>
-      <c r="AS83" t="inlineStr"/>
-      <c r="AT83" t="inlineStr"/>
+      <c r="W83" t="n">
+        <v>1</v>
+      </c>
+      <c r="X83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN83" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>April 2025: An educational facility was taken over by unidentified gang members.</t>
+        </is>
+      </c>
+      <c r="AP83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education Building </t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>Criminal</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>Unspecified gang (Haiti)</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>Firearms</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr">
+        <is>
+          <t>Secondary School</t>
+        </is>
+      </c>
       <c r="AU83" t="inlineStr"/>
       <c r="AV83" t="inlineStr"/>
       <c r="AW83" t="inlineStr"/>
@@ -10527,16 +10785,16 @@
           <t>Centre</t>
         </is>
       </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>Mirebalais</t>
-        </is>
+      <c r="AY83" t="n">
+        <v>19</v>
       </c>
       <c r="AZ83" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA83" t="n">
         <v>3</v>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>HT06</t>
+        </is>
       </c>
       <c r="BB83" t="inlineStr"/>
       <c r="BC83" t="inlineStr">
@@ -10551,12 +10809,12 @@
       </c>
       <c r="BE83" t="inlineStr">
         <is>
-          <t>Viv Ansanm Gang ---- Taliban Gang ---- Canaan Gang</t>
+          <t>Taliban Gang ---- Canaan Gang ---- Viv Ansanm Gang</t>
         </is>
       </c>
       <c r="BF83" t="inlineStr">
         <is>
-          <t>400 Mawozo Gang; Canaan Gang ---- 400 Mawozo Gang; Viv Ansanm Gang ---- 400 Mawozo Gang; Viv Ansanm Gang</t>
+          <t>400 Mawozo Gang; Viv Ansanm Gang ---- 400 Mawozo Gang; Viv Ansanm Gang ---- 400 Mawozo Gang; Canaan Gang</t>
         </is>
       </c>
       <c r="BG83" t="inlineStr">
@@ -10566,20 +10824,25 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>Catholic Christian Group (Haiti); Students (Haiti); Prisoners (Haiti) ---- Catholic Christian Group (Haiti); Students (Haiti)</t>
+          <t>Catholic Christian Group (Haiti); Prisoners (Haiti); Students (Haiti) ---- Catholic Christian Group (Haiti); Students (Haiti) ---- Aid Workers (Haiti); Labor Group (Haiti)</t>
         </is>
       </c>
       <c r="BI83" t="inlineStr">
         <is>
-          <t>On 1 April 2025, in Mirebalais, Centre, for a second consecutive day, gang members attacked the commune and took control of the Mirebalais High School. The criminals fired shots in the directions of residents, killing several people who tried to flee the Mirebalais Hospital, including a security guard. The criminals were identified as affiliates of the Canaan Gang and the 400 Mawozo Gang. This was part of an offensive orchestrated by the Viv Ansanm Gang coalition in reprisal for the resistance of the Trianon self-defense group to gang presence in the area over the weekend (coded separately). Between 31 March and 3 April, at least 30 people were killed and more than 6,000 were displaced as a result of gang attacks in Mirebalais and Saut-d'Eau communes (30 fatalities split across seven events). Between 31 March and 8 April, 19 civilians were killed in Mirebalais village (19 fatalities split across four events). 2 fatalities coded here. ---- On 31 March 2025, in Mirebalais, Centre, in the early morning, several dozen gang members attacked Mirebalais and Trianon (coded separately). Only in Mirebalais, at least 13 killed civilians were identified, including two nuns from the Little Sisters of Saint Therese congregation (Catholic group). They were taking refuge at the Mirebalais National School when the gang members killed them, among others, and injured a girl who was with them. The criminals opened fire on houses, schools, and churches, and set fire to vehicles along the National Road 3. They burned a gas station, the communal market, a part of the Mirebalais police station, and assaulted the Civil Prison. Security forces had abandoned the facilities moments before. The gang members released more than 500 inmates (including the wife of the Pierre VI Gang leader) and killed a prisoner. The facilities were later recovered by security forces after clashes with the gang members (coded separately). Residents claimed that the offensive was a reprisal orchestrated by the Viv Ansanm Gang coalition for the resistance of the Trianon self-defense group to gang presence in the area. The gangsters were identified as affiliates of the Taliban Gang (from Canaan) and the 400 Mawozo Gang. They wore t-shirts with the names of these groups. Between 31 March and 3 April, at least 30 people were killed and more than 6,000 were displaced as a result of gang attacks in Mirebalais and Saut-d'Eau communes (30 fatalities split across seven events). Between 31 March and 8 April, 19 civilians were killed in Mirebalais village (19 fatalities split across four events). 14 coded here. ---- On 31 March 2025, in Trianon, Centre, in the early morning, several dozen gang members attacked residents in Trianon and Mirebalais (coded separately), killing and injuring several people. The gang members opened fire on residents' houses, schools, and churches (Catholic churches), and set fire to vehicles along the National Road 3. Security forces intervened and expelled the criminals (coded separately). Residents claimed that the attack was a reprisal orchestrated by the Viv Ansanm Gang coalition for the resistance of a Trianon self-defense group to gang presence in the area. The gang members were identified as affiliates of the Canaan Gang and the 400 Mawozo Gang. They wore t-shirts with the names of these groups. Between 31 March and 3 April, at least 30 people were killed and more than 6,000 were displaced as a result of gang attacks in Mirebalais and Saut-d'Eau communes. At least 30 fatalities split across seven events, 3 fatalities coded here.</t>
+          <t>On 31 March 2025, in Mirebalais, Centre, in the early morning, several dozen gang members attacked Mirebalais and Trianon (coded separately). Only in Mirebalais, at least 13 killed civilians were identified, including two nuns from the Little Sisters of Saint Therese congregation (Catholic group). They were taking refuge at the Mirebalais National School when the gang members killed them, among others, and injured a girl who was with them. The criminals opened fire on houses, schools, and churches, and set fire to vehicles along the National Road 3. They burned a gas station, the communal market, a part of the Mirebalais police station, and assaulted the Civil Prison. Security forces had abandoned the facilities moments before. The gang members released more than 500 inmates (including the wife of the Pierre VI Gang leader) and killed a prisoner. The facilities were later recovered by security forces after clashes with the gang members (coded separately). Residents claimed that the offensive was a reprisal orchestrated by the Viv Ansanm Gang coalition for the resistance of the Trianon self-defense group to gang presence in the area. The gangsters were identified as affiliates of the Taliban Gang (from Canaan) and the 400 Mawozo Gang. They wore t-shirts with the names of these groups. Between 31 March and 3 April, at least 30 people were killed and more than 6,000 were displaced as a result of gang attacks in Mirebalais and Saut-d'Eau communes (30 fatalities split across seven events). Between 31 March and 8 April, 19 civilians were killed in Mirebalais village (19 fatalities split across four events). 14 coded here. ---- On 31 March 2025, in Trianon, Centre, in the early morning, several dozen gang members attacked residents in Trianon and Mirebalais (coded separately), killing and injuring several people. The gang members opened fire on residents' houses, schools, and churches (Catholic churches), and set fire to vehicles along the National Road 3. Security forces intervened and expelled the criminals (coded separately). Residents claimed that the attack was a reprisal orchestrated by the Viv Ansanm Gang coalition for the resistance of a Trianon self-defense group to gang presence in the area. The gang members were identified as affiliates of the Canaan Gang and the 400 Mawozo Gang. They wore t-shirts with the names of these groups. Between 31 March and 3 April, at least 30 people were killed and more than 6,000 were displaced as a result of gang attacks in Mirebalais and Saut-d'Eau communes. At least 30 fatalities split across seven events, 3 fatalities coded here. ---- On 1 April 2025, in Mirebalais, Centre, for a second consecutive day, gang members attacked the commune and took control of the Mirebalais High School. The criminals fired shots in the direction of residents, killing several people who tried to flee the Mirebalais Hospital, including a security guard. An International Non-Governmental Organization aid worker also died after being injured during an ambush carried out by the gangsters. The criminals were identified as affiliates of the Canaan Gang and the 400 Mawozo Gang. This was part of an offensive orchestrated by the Viv Ansanm Gang coalition in reprisal for the resistance of the Trianon self-defense group to gang presence in the area over the weekend (coded separately). Between 31 March and 3 April, at least 30 people were killed and more than 6,000 were displaced as a result of gang attacks in Mirebalais and Saut-d'Eau communes (30 fatalities split across seven events). Between 31 March and 8 April, 19 civilians were killed in Mirebalais village (19 fatalities split across four events). 2 fatalities coded here.</t>
         </is>
       </c>
       <c r="BJ83" t="inlineStr">
         <is>
-          <t>01 April 2025 ---- 31 March 2025 ---- 31 March 2025</t>
-        </is>
-      </c>
-      <c r="BK83" t="n">
+          <t>2025-03-31 ---- 2025-03-31 ---- 2025-04-01</t>
+        </is>
+      </c>
+      <c r="BK83" t="inlineStr">
+        <is>
+          <t>Mirebalais</t>
+        </is>
+      </c>
+      <c r="BL83" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10600,7 +10863,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>HT0122;HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0712;HT0721;HT0741;HT0914</t>
+          <t>HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0721;HT0741;HT0812;HT0914;HT1014</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -10688,7 +10951,8 @@
       <c r="BH84" t="inlineStr"/>
       <c r="BI84" t="inlineStr"/>
       <c r="BJ84" t="inlineStr"/>
-      <c r="BK84" t="n">
+      <c r="BK84" t="inlineStr"/>
+      <c r="BL84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10709,7 +10973,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>HT0122;HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0712;HT0721;HT0741;HT0914</t>
+          <t>HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0721;HT0741;HT0812;HT0914;HT1014</t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -10797,7 +11061,8 @@
       <c r="BH85" t="inlineStr"/>
       <c r="BI85" t="inlineStr"/>
       <c r="BJ85" t="inlineStr"/>
-      <c r="BK85" t="n">
+      <c r="BK85" t="inlineStr"/>
+      <c r="BL85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10818,7 +11083,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -10906,7 +11171,8 @@
       <c r="BH86" t="inlineStr"/>
       <c r="BI86" t="inlineStr"/>
       <c r="BJ86" t="inlineStr"/>
-      <c r="BK86" t="n">
+      <c r="BK86" t="inlineStr"/>
+      <c r="BL86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10927,7 +11193,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H87" t="n">
@@ -11015,7 +11281,8 @@
       <c r="BH87" t="inlineStr"/>
       <c r="BI87" t="inlineStr"/>
       <c r="BJ87" t="inlineStr"/>
-      <c r="BK87" t="n">
+      <c r="BK87" t="inlineStr"/>
+      <c r="BL87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11036,7 +11303,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -11124,7 +11391,8 @@
       <c r="BH88" t="inlineStr"/>
       <c r="BI88" t="inlineStr"/>
       <c r="BJ88" t="inlineStr"/>
-      <c r="BK88" t="n">
+      <c r="BK88" t="inlineStr"/>
+      <c r="BL88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11145,7 +11413,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>HT0122;HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0712;HT0721;HT0741;HT0914</t>
+          <t>HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0721;HT0741;HT0812;HT0914;HT1014</t>
         </is>
       </c>
       <c r="H89" t="n">
@@ -11233,7 +11501,8 @@
       <c r="BH89" t="inlineStr"/>
       <c r="BI89" t="inlineStr"/>
       <c r="BJ89" t="inlineStr"/>
-      <c r="BK89" t="n">
+      <c r="BK89" t="inlineStr"/>
+      <c r="BL89" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11254,7 +11523,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H90" t="n">
@@ -11342,7 +11611,8 @@
       <c r="BH90" t="inlineStr"/>
       <c r="BI90" t="inlineStr"/>
       <c r="BJ90" t="inlineStr"/>
-      <c r="BK90" t="n">
+      <c r="BK90" t="inlineStr"/>
+      <c r="BL90" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11363,7 +11633,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H91" t="n">
@@ -11443,36 +11713,36 @@
           <t>Sud</t>
         </is>
       </c>
-      <c r="AY91" t="inlineStr">
-        <is>
-          <t>Cayes</t>
-        </is>
+      <c r="AY91" t="n">
+        <v>0</v>
       </c>
       <c r="AZ91" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA91" t="n">
         <v>3</v>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>HT07</t>
+        </is>
       </c>
       <c r="BB91" t="inlineStr"/>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>Riots ---- Riots ---- Protests</t>
+          <t>Protests ---- Riots ---- Riots</t>
         </is>
       </c>
       <c r="BD91" t="inlineStr">
         <is>
-          <t>Violent demonstration ---- Violent demonstration ---- Peaceful protest</t>
+          <t>Peaceful protest ---- Violent demonstration ---- Violent demonstration</t>
         </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
-          <t>Rioters (Haiti) ---- Rioters (Haiti) ---- Protesters (Haiti)</t>
+          <t>Protesters (Haiti) ---- Rioters (Haiti) ---- Rioters (Haiti)</t>
         </is>
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>Students (Haiti) ---- Students (Haiti) ---- Teachers (Haiti)</t>
+          <t>Teachers (Haiti) ---- Students (Haiti) ---- Students (Haiti)</t>
         </is>
       </c>
       <c r="BG91" t="inlineStr">
@@ -11483,15 +11753,20 @@
       <c r="BH91" t="inlineStr"/>
       <c r="BI91" t="inlineStr">
         <is>
-          <t>On 26 March 2025, in Les Cayes, Sud, several dozens of students demonstrated to demand that professors return to classrooms as they have not since a national strike was launched in January. Demonstrating students threw stones against a school to disrupt their activities and forced the closing of other public schools on their path. ---- On 15 January 2025, in Les Cayes, Sud, students from public high schools held a march towards the South departmental office of the Ministry of National Education and Vocational Training (MENFP), on Bergeaud neighborhood, demanding the return of teachers to classrooms after they went on a strike. Police forces intervened and fired tear gas against the demonstrating students to disperse them. Some of them responded by throwing stones against the officers. ---- On 6 January 2025, in Les Cayes, Sud, several scores of teachers held a protest at the Philippe Guerrier high school demanding higher wages, among other claims. The mobilization was part of a teachers' strike.</t>
+          <t>On 6 January 2025, in Les Cayes, Sud, several scores of teachers held a protest at the Philippe Guerrier high school demanding higher wages, among other claims. The mobilization was part of a teachers' strike. ---- On 15 January 2025, in Les Cayes, Sud, students from public high schools held a march towards the South departmental office of the Ministry of National Education and Vocational Training (MENFP), on Bergeaud neighborhood, demanding the return of teachers to classrooms after they went on a strike. Police forces intervened and fired tear gas against the demonstrating students to disperse them. Some of them responded by throwing stones against the officers. ---- On 26 March 2025, in Les Cayes, Sud, several dozens of students demonstrated to demand that professors return to classrooms as they have not since a national strike was launched in January. Demonstrating students threw stones against a school to disrupt their activities and forced the closing of other public schools on their path.</t>
         </is>
       </c>
       <c r="BJ91" t="inlineStr">
         <is>
-          <t>26 March 2025 ---- 15 January 2025 ---- 06 January 2025</t>
-        </is>
-      </c>
-      <c r="BK91" t="n">
+          <t>2025-01-06 ---- 2025-01-15 ---- 2025-03-26</t>
+        </is>
+      </c>
+      <c r="BK91" t="inlineStr">
+        <is>
+          <t>Cayes</t>
+        </is>
+      </c>
+      <c r="BL91" t="n">
         <v>0.2416313143916438</v>
       </c>
     </row>
@@ -11507,12 +11782,12 @@
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>HT0122</t>
+          <t>HT0442</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>HT0122;HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0712;HT0721;HT0741;HT0914</t>
+          <t>HT0122;HT0442;HT0712</t>
         </is>
       </c>
       <c r="H92" t="n">
@@ -11600,7 +11875,8 @@
       <c r="BH92" t="inlineStr"/>
       <c r="BI92" t="inlineStr"/>
       <c r="BJ92" t="inlineStr"/>
-      <c r="BK92" t="n">
+      <c r="BK92" t="inlineStr"/>
+      <c r="BL92" t="n">
         <v>0.2459581235091439</v>
       </c>
     </row>
@@ -11621,7 +11897,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>HT0135;HT0151;HT0152;HT0214;HT0332;HT0713;HT0715;HT0723;HT0733;HT1021;HT1022</t>
+          <t>HT0135;HT0214;HT0413;HT0713;HT1012</t>
         </is>
       </c>
       <c r="H93" t="n">
@@ -11709,7 +11985,8 @@
       <c r="BH93" t="inlineStr"/>
       <c r="BI93" t="inlineStr"/>
       <c r="BJ93" t="inlineStr"/>
-      <c r="BK93" t="n">
+      <c r="BK93" t="inlineStr"/>
+      <c r="BL93" t="n">
         <v>0.2220812182741117</v>
       </c>
     </row>
@@ -11730,7 +12007,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H94" t="n">
@@ -11818,7 +12095,8 @@
       <c r="BH94" t="inlineStr"/>
       <c r="BI94" t="inlineStr"/>
       <c r="BJ94" t="inlineStr"/>
-      <c r="BK94" t="n">
+      <c r="BK94" t="inlineStr"/>
+      <c r="BL94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11839,7 +12117,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>HT0135;HT0151;HT0152;HT0214;HT0332;HT0713;HT0715;HT0723;HT0733;HT1021;HT1022</t>
+          <t>HT0151;HT0152;HT0332;HT0715;HT0723;HT0733;HT1021;HT1022</t>
         </is>
       </c>
       <c r="H95" t="n">
@@ -11927,7 +12205,8 @@
       <c r="BH95" t="inlineStr"/>
       <c r="BI95" t="inlineStr"/>
       <c r="BJ95" t="inlineStr"/>
-      <c r="BK95" t="n">
+      <c r="BK95" t="inlineStr"/>
+      <c r="BL95" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11948,7 +12227,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H96" t="n">
@@ -12036,7 +12315,8 @@
       <c r="BH96" t="inlineStr"/>
       <c r="BI96" t="inlineStr"/>
       <c r="BJ96" t="inlineStr"/>
-      <c r="BK96" t="n">
+      <c r="BK96" t="inlineStr"/>
+      <c r="BL96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12057,7 +12337,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>HT0122;HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0712;HT0721;HT0741;HT0914</t>
+          <t>HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0721;HT0741;HT0812;HT0914;HT1014</t>
         </is>
       </c>
       <c r="H97" t="n">
@@ -12145,7 +12425,8 @@
       <c r="BH97" t="inlineStr"/>
       <c r="BI97" t="inlineStr"/>
       <c r="BJ97" t="inlineStr"/>
-      <c r="BK97" t="n">
+      <c r="BK97" t="inlineStr"/>
+      <c r="BL97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12254,7 +12535,8 @@
       <c r="BH98" t="inlineStr"/>
       <c r="BI98" t="inlineStr"/>
       <c r="BJ98" t="inlineStr"/>
-      <c r="BK98" t="n">
+      <c r="BK98" t="inlineStr"/>
+      <c r="BL98" t="n">
         <v>0.2817669172932331</v>
       </c>
     </row>
@@ -12275,7 +12557,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>HT0135;HT0151;HT0152;HT0214;HT0332;HT0713;HT0715;HT0723;HT0733;HT1021;HT1022</t>
+          <t>HT0151;HT0152;HT0332;HT0715;HT0723;HT0733;HT1021;HT1022</t>
         </is>
       </c>
       <c r="H99" t="n">
@@ -12363,7 +12645,8 @@
       <c r="BH99" t="inlineStr"/>
       <c r="BI99" t="inlineStr"/>
       <c r="BJ99" t="inlineStr"/>
-      <c r="BK99" t="n">
+      <c r="BK99" t="inlineStr"/>
+      <c r="BL99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12384,7 +12667,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H100" t="n">
@@ -12472,7 +12755,8 @@
       <c r="BH100" t="inlineStr"/>
       <c r="BI100" t="inlineStr"/>
       <c r="BJ100" t="inlineStr"/>
-      <c r="BK100" t="n">
+      <c r="BK100" t="inlineStr"/>
+      <c r="BL100" t="n">
         <v>0.2632023403806135</v>
       </c>
     </row>
@@ -12493,7 +12777,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H101" t="n">
@@ -12573,16 +12857,16 @@
           <t>Sud</t>
         </is>
       </c>
-      <c r="AY101" t="inlineStr">
-        <is>
-          <t>Aquin</t>
-        </is>
+      <c r="AY101" t="n">
+        <v>0</v>
       </c>
       <c r="AZ101" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA101" t="n">
         <v>1</v>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>HT07</t>
+        </is>
       </c>
       <c r="BB101" t="inlineStr"/>
       <c r="BC101" t="inlineStr">
@@ -12614,10 +12898,15 @@
       </c>
       <c r="BJ101" t="inlineStr">
         <is>
-          <t>22 January 2025</t>
-        </is>
-      </c>
-      <c r="BK101" t="n">
+          <t>2025-01-22</t>
+        </is>
+      </c>
+      <c r="BK101" t="inlineStr">
+        <is>
+          <t>Aquin</t>
+        </is>
+      </c>
+      <c r="BL101" t="n">
         <v>0.3222556587727332</v>
       </c>
     </row>
@@ -12638,7 +12927,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>HT0135;HT0151;HT0152;HT0214;HT0332;HT0713;HT0715;HT0723;HT0733;HT1021;HT1022</t>
+          <t>HT0151;HT0152;HT0332;HT0715;HT0723;HT0733;HT1021;HT1022</t>
         </is>
       </c>
       <c r="H102" t="n">
@@ -12726,7 +13015,8 @@
       <c r="BH102" t="inlineStr"/>
       <c r="BI102" t="inlineStr"/>
       <c r="BJ102" t="inlineStr"/>
-      <c r="BK102" t="n">
+      <c r="BK102" t="inlineStr"/>
+      <c r="BL102" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12747,7 +13037,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>HT0122;HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0712;HT0721;HT0741;HT0914</t>
+          <t>HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0721;HT0741;HT0812;HT0914;HT1014</t>
         </is>
       </c>
       <c r="H103" t="n">
@@ -12835,7 +13125,8 @@
       <c r="BH103" t="inlineStr"/>
       <c r="BI103" t="inlineStr"/>
       <c r="BJ103" t="inlineStr"/>
-      <c r="BK103" t="n">
+      <c r="BK103" t="inlineStr"/>
+      <c r="BL103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12851,12 +13142,12 @@
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>HT0423</t>
+          <t>HT0821</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0742;HT0811;HT0815;HT0821;HT0822;HT0831;HT0833;HT0834</t>
         </is>
       </c>
       <c r="H104" t="n">
@@ -12944,7 +13235,8 @@
       <c r="BH104" t="inlineStr"/>
       <c r="BI104" t="inlineStr"/>
       <c r="BJ104" t="inlineStr"/>
-      <c r="BK104" t="n">
+      <c r="BK104" t="inlineStr"/>
+      <c r="BL104" t="n">
         <v>0.2434133830729774</v>
       </c>
     </row>
@@ -12965,7 +13257,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H105" t="n">
@@ -13053,7 +13345,8 @@
       <c r="BH105" t="inlineStr"/>
       <c r="BI105" t="inlineStr"/>
       <c r="BJ105" t="inlineStr"/>
-      <c r="BK105" t="n">
+      <c r="BK105" t="inlineStr"/>
+      <c r="BL105" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13074,7 +13367,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H106" t="n">
@@ -13162,7 +13455,8 @@
       <c r="BH106" t="inlineStr"/>
       <c r="BI106" t="inlineStr"/>
       <c r="BJ106" t="inlineStr"/>
-      <c r="BK106" t="n">
+      <c r="BK106" t="inlineStr"/>
+      <c r="BL106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13263,7 +13557,8 @@
       <c r="BH107" t="inlineStr"/>
       <c r="BI107" t="inlineStr"/>
       <c r="BJ107" t="inlineStr"/>
-      <c r="BK107" t="n">
+      <c r="BK107" t="inlineStr"/>
+      <c r="BL107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13284,7 +13579,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H108" t="n">
@@ -13372,7 +13667,8 @@
       <c r="BH108" t="inlineStr"/>
       <c r="BI108" t="inlineStr"/>
       <c r="BJ108" t="inlineStr"/>
-      <c r="BK108" t="n">
+      <c r="BK108" t="inlineStr"/>
+      <c r="BL108" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13393,7 +13689,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>HT0811;HT0815;HT0821;HT0822;HT0831;HT0833;HT0834</t>
+          <t>HT0742;HT0811;HT0815;HT0821;HT0822;HT0831;HT0833;HT0834</t>
         </is>
       </c>
       <c r="H109" t="n">
@@ -13473,36 +13769,36 @@
           <t>Grande-Anse</t>
         </is>
       </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t>Jeremie</t>
-        </is>
+      <c r="AY109" t="n">
+        <v>0</v>
       </c>
       <c r="AZ109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA109" t="n">
         <v>6</v>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>HT08</t>
+        </is>
       </c>
       <c r="BB109" t="inlineStr"/>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>Protests ---- Riots ---- Protests ---- Protests ---- Protests ---- Protests</t>
+          <t>Protests ---- Protests ---- Protests ---- Protests ---- Riots ---- Protests</t>
         </is>
       </c>
       <c r="BD109" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Violent demonstration ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest</t>
+          <t>Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Peaceful protest ---- Violent demonstration ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
-          <t>Protesters (Haiti) ---- Rioters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti)</t>
+          <t>Protesters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti) ---- Rioters (Haiti) ---- Protesters (Haiti)</t>
         </is>
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>Students (Haiti) ---- Students (Haiti) ---- Teachers (Haiti) ---- Students (Haiti) ---- Teachers (Haiti) ---- Students (Haiti)</t>
+          <t>Students (Haiti) ---- Students (Haiti) ---- Teachers (Haiti) ---- Teachers (Haiti) ---- Students (Haiti) ---- Students (Haiti)</t>
         </is>
       </c>
       <c r="BG109" t="inlineStr">
@@ -13513,15 +13809,20 @@
       <c r="BH109" t="inlineStr"/>
       <c r="BI109" t="inlineStr">
         <is>
-          <t>On 10 February 2025, in Jeremie, Grande-Anse, several hundreds of students from public schools took to the streets demanding the return of teachers to classrooms after they went on a strike. ---- Around 3 February 2025 (as reported), in Jeremie, Grande-Anse, public school students held a demonstration in front of the Jean Wesley college building demanding the return of teachers to classrooms. During the mobilization, students threw stones and bottles against the Jean Wesley college and the Saint-Louis de Jeremie college, while police forces fired tear gas to disperse them. Some students were taken to hospital due to tear gas inhalation. ---- On 27 January 2025, in Jeremie, Grande-Anse, teachers from several public schools held a sit-in protest to demand better working conditions. ---- On 15 January 2025, in Jeremie, Grande-Anse, in the morning, hundreds of students, mostly from public schools, took to the streets demanding the return of teachers to classrooms after they went on a strike. The mobilization was held as teachers held a protest over labor-related demands in the commune (coded separately). ---- On 15 January 2025, in Jeremie, Grande-Anse, in the morning, teachers held a protest and marched to the Bordes administrative complex demanding better working conditions. The mobilization was part of a teachers' labor strike. It was held as students held a protest calling for the teachers' return to classrooms (coded separately). ---- On 28 January 2024, in Jeremie, Grande-Anse, high school students held a march demanding the departure of Prime Minister, Ariel Henry, against insecurity and corruption, among other claims. The students took to the street as they joined anti-government mobilizations called by Guy Philippe (a former police officer, senator, convict, paramilitary leader, and warlord who had called on taking the streets and leading a revolution in Haiti).</t>
+          <t>On 28 January 2024, in Jeremie, Grande-Anse, high school students held a march demanding the departure of Prime Minister, Ariel Henry, against insecurity and corruption, among other claims. The students took to the street as they joined anti-government mobilizations called by Guy Philippe (a former police officer, senator, convict, paramilitary leader, and warlord who had called on taking the streets and leading a revolution in Haiti). ---- On 15 January 2025, in Jeremie, Grande-Anse, in the morning, hundreds of students, mostly from public schools, took to the streets demanding the return of teachers to classrooms after they went on a strike. The mobilization was held as teachers held a protest over labor-related demands in the commune (coded separately). ---- On 15 January 2025, in Jeremie, Grande-Anse, in the morning, teachers held a protest and marched to the Bordes administrative complex demanding better working conditions. The mobilization was part of a teachers' labor strike. It was held as students held a protest calling for the teachers' return to classrooms (coded separately). ---- On 27 January 2025, in Jeremie, Grande-Anse, teachers from several public schools held a sit-in protest to demand better working conditions. ---- Around 3 February 2025 (as reported), in Jeremie, Grande-Anse, public school students held a demonstration in front of the Jean Wesley college building demanding the return of teachers to classrooms. During the mobilization, students threw stones and bottles against the Jean Wesley college and the Saint-Louis de Jeremie college, while police forces fired tear gas to disperse them. Some students were taken to hospital due to tear gas inhalation. ---- On 10 February 2025, in Jeremie, Grande-Anse, several hundreds of students from public schools took to the streets demanding the return of teachers to classrooms after they went on a strike.</t>
         </is>
       </c>
       <c r="BJ109" t="inlineStr">
         <is>
-          <t>10 February 2025 ---- 03 February 2025 ---- 27 January 2025 ---- 15 January 2025 ---- 15 January 2025 ---- 28 January 2024</t>
-        </is>
-      </c>
-      <c r="BK109" t="n">
+          <t>2024-01-28 ---- 2025-01-15 ---- 2025-01-15 ---- 2025-01-27 ---- 2025-02-03 ---- 2025-02-10</t>
+        </is>
+      </c>
+      <c r="BK109" t="inlineStr">
+        <is>
+          <t>Jeremie</t>
+        </is>
+      </c>
+      <c r="BL109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13542,7 +13843,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0721;HT0741;HT0812;HT0914;HT1014</t>
         </is>
       </c>
       <c r="H110" t="n">
@@ -13630,7 +13931,8 @@
       <c r="BH110" t="inlineStr"/>
       <c r="BI110" t="inlineStr"/>
       <c r="BJ110" t="inlineStr"/>
-      <c r="BK110" t="n">
+      <c r="BK110" t="inlineStr"/>
+      <c r="BL110" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13731,7 +14033,8 @@
       <c r="BH111" t="inlineStr"/>
       <c r="BI111" t="inlineStr"/>
       <c r="BJ111" t="inlineStr"/>
-      <c r="BK111" t="n">
+      <c r="BK111" t="inlineStr"/>
+      <c r="BL111" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13840,7 +14143,8 @@
       <c r="BH112" t="inlineStr"/>
       <c r="BI112" t="inlineStr"/>
       <c r="BJ112" t="inlineStr"/>
-      <c r="BK112" t="n">
+      <c r="BK112" t="inlineStr"/>
+      <c r="BL112" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13861,7 +14165,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>HT0811;HT0815;HT0821;HT0822;HT0831;HT0833;HT0834</t>
+          <t>HT0742;HT0811;HT0815;HT0821;HT0822;HT0831;HT0833;HT0834</t>
         </is>
       </c>
       <c r="H113" t="n">
@@ -13949,7 +14253,8 @@
       <c r="BH113" t="inlineStr"/>
       <c r="BI113" t="inlineStr"/>
       <c r="BJ113" t="inlineStr"/>
-      <c r="BK113" t="n">
+      <c r="BK113" t="inlineStr"/>
+      <c r="BL113" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13970,7 +14275,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>HT0811;HT0815;HT0821;HT0822;HT0831;HT0833;HT0834</t>
+          <t>HT0742;HT0811;HT0815;HT0821;HT0822;HT0831;HT0833;HT0834</t>
         </is>
       </c>
       <c r="H114" t="n">
@@ -14058,7 +14363,8 @@
       <c r="BH114" t="inlineStr"/>
       <c r="BI114" t="inlineStr"/>
       <c r="BJ114" t="inlineStr"/>
-      <c r="BK114" t="n">
+      <c r="BK114" t="inlineStr"/>
+      <c r="BL114" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14079,7 +14385,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>HT0811;HT0815;HT0821;HT0822;HT0831;HT0833;HT0834</t>
+          <t>HT0742;HT0811;HT0815;HT0821;HT0822;HT0831;HT0833;HT0834</t>
         </is>
       </c>
       <c r="H115" t="n">
@@ -14167,7 +14473,8 @@
       <c r="BH115" t="inlineStr"/>
       <c r="BI115" t="inlineStr"/>
       <c r="BJ115" t="inlineStr"/>
-      <c r="BK115" t="n">
+      <c r="BK115" t="inlineStr"/>
+      <c r="BL115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14276,7 +14583,8 @@
       <c r="BH116" t="inlineStr"/>
       <c r="BI116" t="inlineStr"/>
       <c r="BJ116" t="inlineStr"/>
-      <c r="BK116" t="n">
+      <c r="BK116" t="inlineStr"/>
+      <c r="BL116" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14297,7 +14605,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>HT0811;HT0815;HT0821;HT0822;HT0831;HT0833;HT0834</t>
+          <t>HT0742;HT0811;HT0815;HT0821;HT0822;HT0831;HT0833;HT0834</t>
         </is>
       </c>
       <c r="H117" t="n">
@@ -14385,7 +14693,8 @@
       <c r="BH117" t="inlineStr"/>
       <c r="BI117" t="inlineStr"/>
       <c r="BJ117" t="inlineStr"/>
-      <c r="BK117" t="n">
+      <c r="BK117" t="inlineStr"/>
+      <c r="BL117" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14494,7 +14803,8 @@
       <c r="BH118" t="inlineStr"/>
       <c r="BI118" t="inlineStr"/>
       <c r="BJ118" t="inlineStr"/>
-      <c r="BK118" t="n">
+      <c r="BK118" t="inlineStr"/>
+      <c r="BL118" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14515,7 +14825,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>HT0811;HT0815;HT0821;HT0822;HT0831;HT0833;HT0834</t>
+          <t>HT0742;HT0811;HT0815;HT0821;HT0822;HT0831;HT0833;HT0834</t>
         </is>
       </c>
       <c r="H119" t="n">
@@ -14603,7 +14913,8 @@
       <c r="BH119" t="inlineStr"/>
       <c r="BI119" t="inlineStr"/>
       <c r="BJ119" t="inlineStr"/>
-      <c r="BK119" t="n">
+      <c r="BK119" t="inlineStr"/>
+      <c r="BL119" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14624,7 +14935,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>HT0811;HT0815;HT0821;HT0822;HT0831;HT0833;HT0834</t>
+          <t>HT0742;HT0811;HT0815;HT0821;HT0822;HT0831;HT0833;HT0834</t>
         </is>
       </c>
       <c r="H120" t="n">
@@ -14712,7 +15023,8 @@
       <c r="BH120" t="inlineStr"/>
       <c r="BI120" t="inlineStr"/>
       <c r="BJ120" t="inlineStr"/>
-      <c r="BK120" t="n">
+      <c r="BK120" t="inlineStr"/>
+      <c r="BL120" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14733,7 +15045,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H121" t="n">
@@ -14813,59 +15125,64 @@
           <t>Nord-Ouest</t>
         </is>
       </c>
-      <c r="AY121" t="inlineStr">
-        <is>
-          <t>Port De Paix</t>
-        </is>
+      <c r="AY121" t="n">
+        <v>0</v>
       </c>
       <c r="AZ121" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA121" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>HT09</t>
+        </is>
       </c>
       <c r="BB121" t="inlineStr"/>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>Riots ---- Protests ---- Protests</t>
+          <t>Protests ---- Protests ---- Riots ---- Protests</t>
         </is>
       </c>
       <c r="BD121" t="inlineStr">
         <is>
-          <t>Violent demonstration ---- Peaceful protest ---- Peaceful protest</t>
+          <t>Peaceful protest ---- Peaceful protest ---- Violent demonstration ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BE121" t="inlineStr">
         <is>
-          <t>Rioters (Haiti) ---- Protesters (Haiti) ---- Protesters (Haiti)</t>
+          <t>Protesters (Haiti) ---- Protesters (Haiti) ---- Rioters (Haiti) ---- Protesters (Haiti)</t>
         </is>
       </c>
       <c r="BF121" t="inlineStr">
         <is>
+          <t>Students (Haiti) ---- Health Workers (Haiti); Labor Group (Haiti); Students (Haiti)</t>
+        </is>
+      </c>
+      <c r="BG121" t="inlineStr">
+        <is>
+          <t>Civilians (Haiti)</t>
+        </is>
+      </c>
+      <c r="BH121" t="inlineStr">
+        <is>
           <t>Students (Haiti)</t>
         </is>
       </c>
-      <c r="BG121" t="inlineStr">
-        <is>
-          <t>Civilians (Haiti)</t>
-        </is>
-      </c>
-      <c r="BH121" t="inlineStr">
-        <is>
-          <t>Students (Haiti)</t>
-        </is>
-      </c>
       <c r="BI121" t="inlineStr">
         <is>
-          <t>On 20 January 2025, in Port-de-Paix, Nord-Ouest, students from the Tertullien Guilbaud High School held a demonstration to decry the absence of teachers at classrooms after they went on a labor strike. The students marched to the premises of several schools and threw stones against classrooms. Several students were injured. Police forces intervened (methods unclarified) and took control of the situation. Several injured. ---- On 6 February 2024, in Port-de-Paix, Nord-Ouest, for the second consecutive day, government opponents held a protest demanding the departure of Prime Minister (PM), Ariel Henry. Schools and publics institutions remained their doors closed. This was part of anti-government mobilizations called by Guy Philippe (a former police officer, senator, convict, paramilitary leader, and warlord who had called on taking the streets and leading a revolution in Haiti). ---- On 5 February 2024, in Port-de-Paix, Nord-Ouest, government opponents held a protest demanding the departure of Prime Minister (PM), Ariel Henry. Schools and publics institutions remained their doors closed. The protest, which was part of anti-government mobilizations called by Guy Philippe (a former police officer, senator, convict, paramilitary leader, and warlord who had called on taking the streets and leading a revolution in Haiti).</t>
+          <t>On 5 February 2024, in Port-de-Paix, Nord-Ouest, government opponents held a protest demanding the departure of Prime Minister (PM), Ariel Henry. Schools and publics institutions remained their doors closed. The protest, which was part of anti-government mobilizations called by Guy Philippe (a former police officer, senator, convict, paramilitary leader, and warlord who had called on taking the streets and leading a revolution in Haiti). ---- On 6 February 2024, in Port-de-Paix, Nord-Ouest, for the second consecutive day, government opponents held a protest demanding the departure of Prime Minister (PM), Ariel Henry. Schools and publics institutions remained their doors closed. This was part of anti-government mobilizations called by Guy Philippe (a former police officer, senator, convict, paramilitary leader, and warlord who had called on taking the streets and leading a revolution in Haiti). ---- On 20 January 2025, in Port-de-Paix, Nord-Ouest, students from the Tertullien Guilbaud High School held a demonstration to decry the absence of teachers at classrooms after they went on a labor strike. The students marched to the premises of several schools and threw stones against classrooms. Several students were injured. Police forces intervened (methods unclarified) and took control of the situation. Several injured. ---- On 24 July 2025, in Port-de-Paix, Nord-Ouest, nursing students, health workers, and other hospital staff members held a protest to demand the release of two doctors who were arrested on 22 July. One version stated that they were arrested in connection to a drug case, while another version indicated they were arrested in connection to a killing. Protesters denounced the negative impact of their arrest on the local health system.</t>
         </is>
       </c>
       <c r="BJ121" t="inlineStr">
         <is>
-          <t>20 January 2025 ---- 06 February 2024 ---- 05 February 2024</t>
-        </is>
-      </c>
-      <c r="BK121" t="n">
+          <t>2024-02-05 ---- 2024-02-06 ---- 2025-01-20 ---- 2025-07-24</t>
+        </is>
+      </c>
+      <c r="BK121" t="inlineStr">
+        <is>
+          <t>Port De Paix</t>
+        </is>
+      </c>
+      <c r="BL121" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14966,7 +15283,8 @@
       <c r="BH122" t="inlineStr"/>
       <c r="BI122" t="inlineStr"/>
       <c r="BJ122" t="inlineStr"/>
-      <c r="BK122" t="n">
+      <c r="BK122" t="inlineStr"/>
+      <c r="BL122" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14987,7 +15305,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H123" t="n">
@@ -15075,7 +15393,8 @@
       <c r="BH123" t="inlineStr"/>
       <c r="BI123" t="inlineStr"/>
       <c r="BJ123" t="inlineStr"/>
-      <c r="BK123" t="n">
+      <c r="BK123" t="inlineStr"/>
+      <c r="BL123" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15096,7 +15415,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>HT0122;HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0712;HT0721;HT0741;HT0914</t>
+          <t>HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0721;HT0741;HT0812;HT0914;HT1014</t>
         </is>
       </c>
       <c r="H124" t="n">
@@ -15184,7 +15503,8 @@
       <c r="BH124" t="inlineStr"/>
       <c r="BI124" t="inlineStr"/>
       <c r="BJ124" t="inlineStr"/>
-      <c r="BK124" t="n">
+      <c r="BK124" t="inlineStr"/>
+      <c r="BL124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15205,7 +15525,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H125" t="n">
@@ -15293,7 +15613,8 @@
       <c r="BH125" t="inlineStr"/>
       <c r="BI125" t="inlineStr"/>
       <c r="BJ125" t="inlineStr"/>
-      <c r="BK125" t="n">
+      <c r="BK125" t="inlineStr"/>
+      <c r="BL125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15314,7 +15635,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H126" t="n">
@@ -15402,7 +15723,8 @@
       <c r="BH126" t="inlineStr"/>
       <c r="BI126" t="inlineStr"/>
       <c r="BJ126" t="inlineStr"/>
-      <c r="BK126" t="n">
+      <c r="BK126" t="inlineStr"/>
+      <c r="BL126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15423,7 +15745,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H127" t="n">
@@ -15511,7 +15833,8 @@
       <c r="BH127" t="inlineStr"/>
       <c r="BI127" t="inlineStr"/>
       <c r="BJ127" t="inlineStr"/>
-      <c r="BK127" t="n">
+      <c r="BK127" t="inlineStr"/>
+      <c r="BL127" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15612,7 +15935,8 @@
       <c r="BH128" t="inlineStr"/>
       <c r="BI128" t="inlineStr"/>
       <c r="BJ128" t="inlineStr"/>
-      <c r="BK128" t="n">
+      <c r="BK128" t="inlineStr"/>
+      <c r="BL128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15633,7 +15957,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H129" t="n">
@@ -15721,7 +16045,8 @@
       <c r="BH129" t="inlineStr"/>
       <c r="BI129" t="inlineStr"/>
       <c r="BJ129" t="inlineStr"/>
-      <c r="BK129" t="n">
+      <c r="BK129" t="inlineStr"/>
+      <c r="BL129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15742,7 +16067,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>HT0321;HT0362;HT0411;HT0413;HT0421;HT0423;HT0431;HT0432;HT0434;HT0442;HT0443;HT0742;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H130" t="n">
@@ -15830,7 +16155,8 @@
       <c r="BH130" t="inlineStr"/>
       <c r="BI130" t="inlineStr"/>
       <c r="BJ130" t="inlineStr"/>
-      <c r="BK130" t="n">
+      <c r="BK130" t="inlineStr"/>
+      <c r="BL130" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15851,7 +16177,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -15931,31 +16257,31 @@
           <t>Nippes</t>
         </is>
       </c>
-      <c r="AY131" t="inlineStr">
-        <is>
-          <t>Miragoane</t>
-        </is>
+      <c r="AY131" t="n">
+        <v>0</v>
       </c>
       <c r="AZ131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA131" t="n">
         <v>2</v>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>HT10</t>
+        </is>
       </c>
       <c r="BB131" t="inlineStr"/>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>Protests ---- Riots</t>
+          <t>Riots ---- Protests</t>
         </is>
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>Peaceful protest ---- Violent demonstration</t>
+          <t>Violent demonstration ---- Peaceful protest</t>
         </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
-          <t>Protesters (Haiti) ---- Rioters (Haiti)</t>
+          <t>Rioters (Haiti) ---- Protesters (Haiti)</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
@@ -15975,15 +16301,20 @@
       </c>
       <c r="BI131" t="inlineStr">
         <is>
-          <t>On 14 January 2025, in Saint Michel du Sud, Nippes, students from the Saint-Michel des Nippes high school took to the streets demanding the return of teachers to classrooms after they went on a strike. Protesters blocked roads in the area. ---- On 13 January 2025, in Miragoane, Nippes, students from the Jeunes Filles public high school held a demonstration against the absence of teachers and calling for their return to classrooms after they went on a strike. During the mobilization, demonstrators clashed with another group of students from the Lumiere private college as they refused to join the mobilization. Clashes involved the throwing of stones and bottles. At least three students from the private institution were injured. Several others fainted. Police forces intervened and fired shots into the air to disperse the rioters. 3 injured.</t>
+          <t>On 13 January 2025, in Miragoane, Nippes, students from the Jeunes Filles public high school held a demonstration against the absence of teachers and calling for their return to classrooms after they went on a strike. During the mobilization, demonstrators clashed with another group of students from the Lumiere private college as they refused to join the mobilization. Clashes involved the throwing of stones and bottles. At least three students from the private institution were injured. Several others fainted. Police forces intervened and fired shots into the air to disperse the rioters. 3 injured. ---- On 14 January 2025, in Saint Michel du Sud, Nippes, students from the Saint-Michel des Nippes high school took to the streets demanding the return of teachers to classrooms after they went on a strike. Protesters blocked roads in the area.</t>
         </is>
       </c>
       <c r="BJ131" t="inlineStr">
         <is>
-          <t>14 January 2025 ---- 13 January 2025</t>
-        </is>
-      </c>
-      <c r="BK131" t="n">
+          <t>2025-01-13 ---- 2025-01-14</t>
+        </is>
+      </c>
+      <c r="BK131" t="inlineStr">
+        <is>
+          <t>Miragoane</t>
+        </is>
+      </c>
+      <c r="BL131" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15999,12 +16330,12 @@
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>HT0111</t>
+          <t>HT0214</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0135;HT0214;HT0413;HT0713;HT1012</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -16092,7 +16423,8 @@
       <c r="BH132" t="inlineStr"/>
       <c r="BI132" t="inlineStr"/>
       <c r="BJ132" t="inlineStr"/>
-      <c r="BK132" t="n">
+      <c r="BK132" t="inlineStr"/>
+      <c r="BL132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16113,7 +16445,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H133" t="n">
@@ -16201,7 +16533,8 @@
       <c r="BH133" t="inlineStr"/>
       <c r="BI133" t="inlineStr"/>
       <c r="BJ133" t="inlineStr"/>
-      <c r="BK133" t="n">
+      <c r="BK133" t="inlineStr"/>
+      <c r="BL133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16217,12 +16550,12 @@
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>HT0121</t>
+          <t>HT0342</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0342;HT0412;HT0422;HT0613;HT0622;HT0623;HT0641;HT0721;HT0741;HT0812;HT0914;HT1014</t>
         </is>
       </c>
       <c r="H134" t="n">
@@ -16310,7 +16643,8 @@
       <c r="BH134" t="inlineStr"/>
       <c r="BI134" t="inlineStr"/>
       <c r="BJ134" t="inlineStr"/>
-      <c r="BK134" t="n">
+      <c r="BK134" t="inlineStr"/>
+      <c r="BL134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16331,7 +16665,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>HT0135;HT0151;HT0152;HT0214;HT0332;HT0713;HT0715;HT0723;HT0733;HT1021;HT1022</t>
+          <t>HT0151;HT0152;HT0332;HT0715;HT0723;HT0733;HT1021;HT1022</t>
         </is>
       </c>
       <c r="H135" t="n">
@@ -16419,7 +16753,8 @@
       <c r="BH135" t="inlineStr"/>
       <c r="BI135" t="inlineStr"/>
       <c r="BJ135" t="inlineStr"/>
-      <c r="BK135" t="n">
+      <c r="BK135" t="inlineStr"/>
+      <c r="BL135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16440,7 +16775,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>HT0135;HT0151;HT0152;HT0214;HT0332;HT0713;HT0715;HT0723;HT0733;HT1021;HT1022</t>
+          <t>HT0151;HT0152;HT0332;HT0715;HT0723;HT0733;HT1021;HT1022</t>
         </is>
       </c>
       <c r="H136" t="n">
@@ -16528,7 +16863,8 @@
       <c r="BH136" t="inlineStr"/>
       <c r="BI136" t="inlineStr"/>
       <c r="BJ136" t="inlineStr"/>
-      <c r="BK136" t="n">
+      <c r="BK136" t="inlineStr"/>
+      <c r="BL136" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16549,7 +16885,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0323;HT0361;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT1011;HT1012;HT1013;HT1023</t>
+          <t>HT0111;HT0114;HT0117;HT0118;HT0131;HT0211;HT0212;HT0213;HT0221;HT0231;HT0233;HT0311;HT0321;HT0323;HT0361;HT0362;HT0411;HT0421;HT0423;HT0431;HT0432;HT0434;HT0443;HT0611;HT0612;HT0614;HT0621;HT0631;HT0632;HT0633;HT0711;HT0714;HT0731;HT0732;HT0911;HT0913;HT0921;HT0922;HT0931;HT0933;HT0934;HT1011;HT1013;HT1023</t>
         </is>
       </c>
       <c r="H137" t="n">
@@ -16637,7 +16973,8 @@
       <c r="BH137" t="inlineStr"/>
       <c r="BI137" t="inlineStr"/>
       <c r="BJ137" t="inlineStr"/>
-      <c r="BK137" t="n">
+      <c r="BK137" t="inlineStr"/>
+      <c r="BL137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16658,7 +16995,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H138" t="n">
@@ -16746,7 +17083,8 @@
       <c r="BH138" t="inlineStr"/>
       <c r="BI138" t="inlineStr"/>
       <c r="BJ138" t="inlineStr"/>
-      <c r="BK138" t="n">
+      <c r="BK138" t="inlineStr"/>
+      <c r="BL138" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16767,7 +17105,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H139" t="n">
@@ -16855,7 +17193,8 @@
       <c r="BH139" t="inlineStr"/>
       <c r="BI139" t="inlineStr"/>
       <c r="BJ139" t="inlineStr"/>
-      <c r="BK139" t="n">
+      <c r="BK139" t="inlineStr"/>
+      <c r="BL139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16876,7 +17215,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H140" t="n">
@@ -16964,7 +17303,8 @@
       <c r="BH140" t="inlineStr"/>
       <c r="BI140" t="inlineStr"/>
       <c r="BJ140" t="inlineStr"/>
-      <c r="BK140" t="n">
+      <c r="BK140" t="inlineStr"/>
+      <c r="BL140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16985,7 +17325,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT0812;HT1014;HT1024;HT1025;HT1031;HT1032</t>
+          <t>HT0113;HT0121;HT0123;HT0232;HT0312;HT0313;HT0322;HT0331;HT0341;HT0344;HT0351;HT0371;HT0433;HT0441;HT0642;HT0716;HT0743;HT0751;HT0753;HT1024;HT1025;HT1031;HT1032</t>
         </is>
       </c>
       <c r="H141" t="n">
@@ -17073,7 +17413,8 @@
       <c r="BH141" t="inlineStr"/>
       <c r="BI141" t="inlineStr"/>
       <c r="BJ141" t="inlineStr"/>
-      <c r="BK141" t="n">
+      <c r="BK141" t="inlineStr"/>
+      <c r="BL141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17083,10 +17424,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C9824523CAB29F4DA646F20BAFE41B4C" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c972c102b01d47663811fb2ebdbd1e4">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" xmlns:ns3="14cbb838-50ff-4dab-9c3f-cddf75f03c13" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bd0e8b72e466adcc572d3af37c1ebe05" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6"/>
-    <xsd:import namespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100DE51FB2AFBB2DD429D3D11FE759FFC43" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1354c8e90e28409d311bbba5db8dc335">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4877444-78fa-4cfa-bafc-d6c64fafc061" xmlns:ns3="d0fa6634-326e-4532-91a2-52bea7ac9212" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dbb4473bd7833dc3543803a005841490" ns2:_="" ns3:_="">
+    <xsd:import namespace="f4877444-78fa-4cfa-bafc-d6c64fafc061"/>
+    <xsd:import namespace="d0fa6634-326e-4532-91a2-52bea7ac9212"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -17098,13 +17439,15 @@
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
@@ -17113,7 +17456,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5940141-1bc9-4c17-b1bc-e50f6b2083d6" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f4877444-78fa-4cfa-bafc-d6c64fafc061" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -17131,52 +17474,57 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="14" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="18" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4d06f0b5-5743-41f2-90d3-b12c8ffc7f36" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="20" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="21" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="22" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="18" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="19" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="14cbb838-50ff-4dab-9c3f-cddf75f03c13" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d0fa6634-326e-4532-91a2-52bea7ac9212" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="SharedWithUsers" ma:index="11" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
@@ -17204,6 +17552,17 @@
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="19" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{d6bd4e25-e667-4943-8e38-5db701f530ee}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d0fa6634-326e-4532-91a2-52bea7ac9212">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -17317,7 +17676,8 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5940141-1bc9-4c17-b1bc-e50f6b2083d6">
+    <TaxCatchAll xmlns="d0fa6634-326e-4532-91a2-52bea7ac9212" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f4877444-78fa-4cfa-bafc-d6c64fafc061">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
@@ -17325,13 +17685,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F953BA0-8BB6-424E-97FA-73490F7D4190}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A321093A-2951-4598-929A-9F8AB3B918A8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{988F30C0-EA42-4B77-B2CF-73CE1FAF7A62}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498BFF9C-C835-466C-BDB3-0562C8C6D579}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D49319D7-322A-4DDD-880E-58EBD2679A15}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{635E6B21-67DF-4E82-9FC2-744BBDAD4705}"/>
 </file>
--- a/context_DB/HTI_context_db.xlsx
+++ b/context_DB/HTI_context_db.xlsx
@@ -17685,13 +17685,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A321093A-2951-4598-929A-9F8AB3B918A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0185E63-B234-418F-B60F-49E83AC53909}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{498BFF9C-C835-466C-BDB3-0562C8C6D579}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CDC13C4-5B1F-4CE1-9755-AE3240543DD2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{635E6B21-67DF-4E82-9FC2-744BBDAD4705}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C60DAA9-855A-42EC-8DD0-6BEDB12F2FC7}"/>
 </file>